--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03B19D2-5163-6A4C-8503-2C0A84A95200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC71A17-F200-454D-AB46-48593B58EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1455</v>
+        <v>1545</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1170</v>
+        <v>1260</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2528,6 +2528,12 @@
       </c>
       <c r="EV2" t="s">
         <v>139</v>
+      </c>
+      <c r="EY2">
+        <v>90</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>110</v>
       </c>
       <c r="FC2">
         <v>90</v>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C29" si="2">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
@@ -2598,7 +2604,7 @@
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E29" si="4">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F30" si="5">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
@@ -2606,11 +2612,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G29" si="6">SUM(H3:I3)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H29" si="7">COUNTIF(AI3:PR3,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I29" si="8">COUNTIF(AI3:PR3,"R")</f>
@@ -2654,11 +2660,11 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S29" si="18">SUM(T3:U3)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" ref="T3:T29" si="19">COUNTIF(IU3:PR3,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" ref="U3:U29" si="20">COUNTIF(IU3:PR3,"R")</f>
@@ -2767,6 +2773,9 @@
       <c r="EV3" t="s">
         <v>139</v>
       </c>
+      <c r="EZ3" t="s">
+        <v>139</v>
+      </c>
       <c r="FD3" t="s">
         <v>139</v>
       </c>
@@ -2819,6 +2828,12 @@
         <v>90</v>
       </c>
       <c r="KN3" t="s">
+        <v>110</v>
+      </c>
+      <c r="KQ3">
+        <v>90</v>
+      </c>
+      <c r="KR3" t="s">
         <v>110</v>
       </c>
       <c r="ME3">
@@ -2829,11 +2844,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2886,7 +2901,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2902,7 +2917,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3058,6 +3073,9 @@
       </c>
       <c r="EV4" t="s">
         <v>110</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>138</v>
       </c>
       <c r="FD4" t="s">
         <v>139</v>
@@ -3152,11 +3170,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3172,7 +3190,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
@@ -3180,7 +3198,7 @@
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="9"/>
@@ -3188,7 +3206,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
@@ -3196,7 +3214,7 @@
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="13"/>
@@ -3383,6 +3401,12 @@
       </c>
       <c r="EV5" t="s">
         <v>110</v>
+      </c>
+      <c r="EY5">
+        <v>1</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>136</v>
       </c>
       <c r="FC5">
         <v>90</v>
@@ -3658,6 +3682,9 @@
       <c r="EV6" t="s">
         <v>139</v>
       </c>
+      <c r="EZ6" t="s">
+        <v>139</v>
+      </c>
       <c r="FD6" t="s">
         <v>139</v>
       </c>
@@ -3696,11 +3723,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3721,11 +3748,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>1758</v>
+        <v>1848</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>913</v>
+        <v>1003</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3741,11 +3768,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3757,11 +3784,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -3943,6 +3970,12 @@
       </c>
       <c r="EV7" t="s">
         <v>139</v>
+      </c>
+      <c r="EY7">
+        <v>90</v>
+      </c>
+      <c r="EZ7" t="s">
+        <v>110</v>
       </c>
       <c r="FC7">
         <v>90</v>
@@ -4233,6 +4266,9 @@
       <c r="EV8" t="s">
         <v>139</v>
       </c>
+      <c r="EZ8" t="s">
+        <v>139</v>
+      </c>
       <c r="FD8" t="s">
         <v>139</v>
       </c>
@@ -4316,11 +4352,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4341,11 +4377,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>1867</v>
+        <v>1957</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1111</v>
+        <v>1201</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4361,11 +4397,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4377,11 +4413,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4586,6 +4622,12 @@
         <v>85</v>
       </c>
       <c r="EV9" t="s">
+        <v>110</v>
+      </c>
+      <c r="EY9">
+        <v>90</v>
+      </c>
+      <c r="EZ9" t="s">
         <v>110</v>
       </c>
       <c r="FC9">
@@ -4669,11 +4711,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1151</v>
+        <v>1241</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>551</v>
+        <v>641</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4689,11 +4731,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4705,11 +4747,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -4893,6 +4935,12 @@
         <v>67</v>
       </c>
       <c r="EV10" t="s">
+        <v>110</v>
+      </c>
+      <c r="EY10">
+        <v>90</v>
+      </c>
+      <c r="EZ10" t="s">
         <v>110</v>
       </c>
       <c r="FC10">
@@ -4979,7 +5027,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1034</v>
+        <v>1124</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
@@ -4991,7 +5039,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="4"/>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="F11">
         <f t="shared" si="5"/>
@@ -4999,11 +5047,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
@@ -5047,11 +5095,11 @@
       </c>
       <c r="S11">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="20"/>
@@ -5205,6 +5253,9 @@
       <c r="EV11" t="s">
         <v>139</v>
       </c>
+      <c r="EZ11" t="s">
+        <v>139</v>
+      </c>
       <c r="FD11" t="s">
         <v>139</v>
       </c>
@@ -5259,13 +5310,19 @@
       <c r="KN11" t="s">
         <v>110</v>
       </c>
+      <c r="KQ11">
+        <v>90</v>
+      </c>
+      <c r="KR11" t="s">
+        <v>110</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="33"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="34"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="35"/>
@@ -5720,6 +5777,9 @@
       <c r="EV13" t="s">
         <v>139</v>
       </c>
+      <c r="EZ13" t="s">
+        <v>139</v>
+      </c>
       <c r="FD13" t="s">
         <v>139</v>
       </c>
@@ -5746,11 +5806,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -5771,11 +5831,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -5791,7 +5851,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
@@ -5799,7 +5859,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
@@ -5807,7 +5867,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
@@ -5815,7 +5875,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
@@ -6032,6 +6092,12 @@
       </c>
       <c r="EV14" t="s">
         <v>110</v>
+      </c>
+      <c r="EY14">
+        <v>1</v>
+      </c>
+      <c r="EZ14" t="s">
+        <v>136</v>
       </c>
       <c r="FC14">
         <v>7</v>
@@ -6120,7 +6186,7 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1306</v>
+        <v>1396</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
@@ -6132,7 +6198,7 @@
       </c>
       <c r="E15">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F15">
         <f t="shared" si="5"/>
@@ -6140,11 +6206,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6188,11 +6254,11 @@
       </c>
       <c r="S15">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" s="3">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" s="3">
         <f t="shared" si="20"/>
@@ -6385,6 +6451,9 @@
       <c r="EV15" t="s">
         <v>136</v>
       </c>
+      <c r="EZ15" t="s">
+        <v>139</v>
+      </c>
       <c r="FC15">
         <v>45</v>
       </c>
@@ -6442,13 +6511,19 @@
       <c r="KF15" t="s">
         <v>110</v>
       </c>
+      <c r="KQ15">
+        <v>90</v>
+      </c>
+      <c r="KR15" t="s">
+        <v>110</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="35"/>
@@ -7107,11 +7182,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7127,7 +7202,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
@@ -7135,7 +7210,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="9"/>
@@ -7143,7 +7218,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
@@ -7151,7 +7226,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="13"/>
@@ -7359,6 +7434,12 @@
       </c>
       <c r="EV18" t="s">
         <v>110</v>
+      </c>
+      <c r="EY18">
+        <v>27</v>
+      </c>
+      <c r="EZ18" t="s">
+        <v>136</v>
       </c>
       <c r="FD18" t="s">
         <v>139</v>
@@ -7441,7 +7522,7 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>975</v>
+        <v>1037</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -7453,7 +7534,7 @@
       </c>
       <c r="E19">
         <f t="shared" si="4"/>
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="F19">
         <f t="shared" si="5"/>
@@ -7461,11 +7542,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
@@ -7509,11 +7590,11 @@
       </c>
       <c r="S19">
         <f>SUM(T19:U19)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="20"/>
@@ -7667,6 +7748,9 @@
       <c r="EV19" t="s">
         <v>138</v>
       </c>
+      <c r="EZ19" t="s">
+        <v>139</v>
+      </c>
       <c r="FC19">
         <v>69</v>
       </c>
@@ -7727,13 +7811,19 @@
       <c r="KF19" t="s">
         <v>110</v>
       </c>
+      <c r="KQ19">
+        <v>62</v>
+      </c>
+      <c r="KR19" t="s">
+        <v>110</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="34"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="35"/>
@@ -7754,11 +7844,11 @@
       </c>
       <c r="B20">
         <f t="shared" si="37"/>
-        <v>1887</v>
+        <v>1950</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
-        <v>1224</v>
+        <v>1287</v>
       </c>
       <c r="D20">
         <f t="shared" si="3"/>
@@ -7774,11 +7864,11 @@
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="8"/>
@@ -7790,11 +7880,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="12"/>
@@ -8033,6 +8123,12 @@
       </c>
       <c r="EW20">
         <v>1</v>
+      </c>
+      <c r="EY20">
+        <v>63</v>
+      </c>
+      <c r="EZ20" t="s">
+        <v>110</v>
       </c>
       <c r="FC20">
         <v>90</v>
@@ -8368,11 +8464,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2368</v>
+        <v>2457</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1349</v>
+        <v>1438</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8388,11 +8484,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8404,11 +8500,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -8460,11 +8556,11 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z22" s="4">
         <f t="shared" si="24"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <f t="shared" si="25"/>
@@ -8472,7 +8568,7 @@
       </c>
       <c r="AB22">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC22">
         <f t="shared" si="27"/>
@@ -8638,6 +8734,15 @@
       </c>
       <c r="EV22" t="s">
         <v>110</v>
+      </c>
+      <c r="EY22">
+        <v>89</v>
+      </c>
+      <c r="EZ22" t="s">
+        <v>110</v>
+      </c>
+      <c r="FB22">
+        <v>1</v>
       </c>
       <c r="FC22">
         <v>90</v>
@@ -8952,11 +9057,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>1907</v>
+        <v>1997</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -8972,11 +9077,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -8988,11 +9093,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9188,6 +9293,12 @@
         <v>90</v>
       </c>
       <c r="EV24" t="s">
+        <v>110</v>
+      </c>
+      <c r="EY24">
+        <v>90</v>
+      </c>
+      <c r="EZ24" t="s">
         <v>110</v>
       </c>
       <c r="FC24">
@@ -9792,6 +9903,9 @@
       <c r="EV26" t="s">
         <v>139</v>
       </c>
+      <c r="EZ26" t="s">
+        <v>139</v>
+      </c>
       <c r="FD26" t="s">
         <v>139</v>
       </c>
@@ -9869,11 +9983,11 @@
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -9894,11 +10008,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1387</v>
+        <v>1477</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>892</v>
+        <v>982</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -9914,11 +10028,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -9930,11 +10044,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10085,6 +10199,12 @@
         <v>90</v>
       </c>
       <c r="EV27" t="s">
+        <v>110</v>
+      </c>
+      <c r="EY27">
+        <v>90</v>
+      </c>
+      <c r="EZ27" t="s">
         <v>110</v>
       </c>
       <c r="FC27">
@@ -10162,7 +10282,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="37"/>
-        <v>1295</v>
+        <v>1385</v>
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
@@ -10174,7 +10294,7 @@
       </c>
       <c r="E28">
         <f t="shared" si="4"/>
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="F28">
         <f t="shared" si="5"/>
@@ -10182,11 +10302,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="8"/>
@@ -10230,11 +10350,11 @@
       </c>
       <c r="S28">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" s="3">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" si="20"/>
@@ -10361,6 +10481,9 @@
       <c r="EV28" t="s">
         <v>136</v>
       </c>
+      <c r="EZ28" t="s">
+        <v>139</v>
+      </c>
       <c r="FD28" t="s">
         <v>139</v>
       </c>
@@ -10421,13 +10544,19 @@
       <c r="KN28" t="s">
         <v>110</v>
       </c>
+      <c r="KQ28">
+        <v>90</v>
+      </c>
+      <c r="KR28" t="s">
+        <v>110</v>
+      </c>
       <c r="PS28" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PT28" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU28" s="3">
         <f t="shared" si="35"/>
@@ -10448,11 +10577,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>579</v>
+        <v>669</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>339</v>
+        <v>429</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -10468,11 +10597,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -10484,11 +10613,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -10625,6 +10754,12 @@
       </c>
       <c r="EX29">
         <v>1</v>
+      </c>
+      <c r="EY29">
+        <v>90</v>
+      </c>
+      <c r="EZ29" t="s">
+        <v>110</v>
       </c>
       <c r="FC29">
         <v>21</v>
@@ -10695,11 +10830,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="67">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>298</v>
+        <v>361</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="68">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="69">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -10715,11 +10850,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="71">SUM(H30:I30)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="72">COUNTIF(AI30:PR30,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="73">COUNTIF(AI30:PR30,"R")</f>
@@ -10731,11 +10866,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="75">SUM(L30:M30)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="76">COUNTIF(CY30:GX30,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="77">COUNTIF(CY30:GX30,"R")</f>
@@ -10845,6 +10980,12 @@
       </c>
       <c r="EV30" t="s">
         <v>136</v>
+      </c>
+      <c r="EY30">
+        <v>63</v>
+      </c>
+      <c r="EZ30" t="s">
+        <v>110</v>
       </c>
       <c r="FC30">
         <v>45</v>
@@ -10891,11 +11032,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -10911,11 +11052,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -10927,11 +11068,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -10975,11 +11116,11 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
@@ -10991,7 +11132,7 @@
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
@@ -11023,6 +11164,15 @@
       </c>
       <c r="EN31" t="s">
         <v>139</v>
+      </c>
+      <c r="EY31">
+        <v>89</v>
+      </c>
+      <c r="EZ31" t="s">
+        <v>110</v>
+      </c>
+      <c r="FA31">
+        <v>2</v>
       </c>
       <c r="FC31">
         <v>69</v>
@@ -11066,11 +11216,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11078,7 +11228,7 @@
       </c>
       <c r="E32">
         <f t="shared" ref="E32" si="145">SUM(IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F32">
         <f t="shared" ref="F32" si="146">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32)</f>
@@ -11086,15 +11236,15 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -11102,7 +11252,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -11110,7 +11260,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -11134,11 +11284,11 @@
       </c>
       <c r="S32">
         <f t="shared" ref="S32" si="159">SUM(T32:U32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="3">
         <f t="shared" ref="T32" si="160">COUNTIF(IU32:PR32,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="3">
         <f t="shared" ref="U32" si="161">COUNTIF(IU32:PR32,"R")</f>
@@ -11196,6 +11346,12 @@
         <f t="shared" ref="AH32" si="174">SUM(IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
         <v>0</v>
       </c>
+      <c r="EY32">
+        <v>27</v>
+      </c>
+      <c r="EZ32" t="s">
+        <v>136</v>
+      </c>
       <c r="FC32">
         <v>21</v>
       </c>
@@ -11207,6 +11363,12 @@
       </c>
       <c r="FH32" t="s">
         <v>136</v>
+      </c>
+      <c r="KQ32">
+        <v>90</v>
+      </c>
+      <c r="KR32" t="s">
+        <v>110</v>
       </c>
       <c r="PS32" s="3">
         <f t="shared" ref="PS32" si="175">COUNTIF(AI32:PR32,"HG")</f>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC71A17-F200-454D-AB46-48593B58EE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5768A0A-4701-E549-83C2-96040370428D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1545</v>
+        <v>1635</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1260</v>
+        <v>1350</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2545,6 +2545,12 @@
         <v>90</v>
       </c>
       <c r="FH2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO2">
+        <v>90</v>
+      </c>
+      <c r="FP2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2782,6 +2788,9 @@
       <c r="FH3" t="s">
         <v>139</v>
       </c>
+      <c r="FP3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2844,11 +2853,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2869,7 +2878,7 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B29" si="37">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
-        <v>1335</v>
+        <v>1425</v>
       </c>
       <c r="C4">
         <f t="shared" si="2"/>
@@ -2881,7 +2890,7 @@
       </c>
       <c r="E4">
         <f t="shared" si="4"/>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="F4">
         <f t="shared" si="5"/>
@@ -2889,11 +2898,11 @@
       </c>
       <c r="G4">
         <f t="shared" ref="G4" si="38">SUM(H4:I4)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="39">COUNTIF(AI4:PR4,"T")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="40">COUNTIF(AI4:PR4,"R")</f>
@@ -2937,11 +2946,11 @@
       </c>
       <c r="S4">
         <f t="shared" ref="S4" si="50">SUM(T4:U4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="20"/>
@@ -3083,6 +3092,9 @@
       <c r="FH4" t="s">
         <v>139</v>
       </c>
+      <c r="FP4" t="s">
+        <v>139</v>
+      </c>
       <c r="GY4">
         <v>90</v>
       </c>
@@ -3141,15 +3153,21 @@
         <v>90</v>
       </c>
       <c r="KF4" t="s">
+        <v>110</v>
+      </c>
+      <c r="KU4">
+        <v>90</v>
+      </c>
+      <c r="KV4" t="s">
         <v>110</v>
       </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="63">COUNTIF(AI4:PR4,"HG")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="64">COUNTIF(CY4:GX4,"HG")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="65">COUNTIF(GY4:IT4,"HG")</f>
@@ -3170,11 +3188,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1293</v>
+        <v>1383</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>683</v>
+        <v>773</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3190,11 +3208,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3206,11 +3224,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3419,6 +3437,12 @@
       </c>
       <c r="FH5" t="s">
         <v>136</v>
+      </c>
+      <c r="FO5">
+        <v>90</v>
+      </c>
+      <c r="FP5" t="s">
+        <v>110</v>
       </c>
       <c r="HD5" t="s">
         <v>139</v>
@@ -3691,6 +3715,9 @@
       <c r="FH6" t="s">
         <v>139</v>
       </c>
+      <c r="FP6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3723,11 +3750,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3748,11 +3775,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>1848</v>
+        <v>1938</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1003</v>
+        <v>1093</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3768,11 +3795,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3784,11 +3811,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -3832,11 +3859,11 @@
       </c>
       <c r="W7" s="3">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="23"/>
@@ -3848,7 +3875,7 @@
       </c>
       <c r="AA7">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB7">
         <f t="shared" si="26"/>
@@ -3988,6 +4015,15 @@
       </c>
       <c r="FH7" t="s">
         <v>110</v>
+      </c>
+      <c r="FO7">
+        <v>90</v>
+      </c>
+      <c r="FP7" t="s">
+        <v>110</v>
+      </c>
+      <c r="FQ7">
+        <v>1</v>
       </c>
       <c r="GY7">
         <v>90</v>
@@ -4275,6 +4311,9 @@
       <c r="FH8" t="s">
         <v>139</v>
       </c>
+      <c r="FP8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4352,11 +4391,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4377,11 +4416,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>1957</v>
+        <v>2047</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1201</v>
+        <v>1291</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4397,11 +4436,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4413,11 +4452,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4640,6 +4679,12 @@
         <v>90</v>
       </c>
       <c r="FH9" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO9">
+        <v>90</v>
+      </c>
+      <c r="FP9" t="s">
         <v>110</v>
       </c>
       <c r="HC9">
@@ -4711,11 +4756,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1241</v>
+        <v>1331</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>641</v>
+        <v>731</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4731,11 +4776,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4747,11 +4792,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -4953,6 +4998,12 @@
         <v>90</v>
       </c>
       <c r="FH10" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO10">
+        <v>90</v>
+      </c>
+      <c r="FP10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5027,7 +5078,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1124</v>
+        <v>1214</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
@@ -5039,7 +5090,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="F11">
         <f t="shared" si="5"/>
@@ -5047,11 +5098,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
@@ -5095,11 +5146,11 @@
       </c>
       <c r="S11">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="19"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="20"/>
@@ -5262,6 +5313,9 @@
       <c r="FH11" t="s">
         <v>139</v>
       </c>
+      <c r="FP11" t="s">
+        <v>139</v>
+      </c>
       <c r="GY11">
         <v>90</v>
       </c>
@@ -5316,13 +5370,19 @@
       <c r="KR11" t="s">
         <v>110</v>
       </c>
+      <c r="KU11">
+        <v>90</v>
+      </c>
+      <c r="KV11" t="s">
+        <v>110</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="33"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="34"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="35"/>
@@ -5786,6 +5846,9 @@
       <c r="FH13" t="s">
         <v>139</v>
       </c>
+      <c r="FP13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -5806,11 +5869,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -5831,11 +5894,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>1693</v>
+        <v>1805</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>865</v>
+        <v>887</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -5843,7 +5906,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <f t="shared" si="5"/>
@@ -5851,15 +5914,15 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
@@ -5867,7 +5930,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
@@ -5875,7 +5938,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
@@ -5899,11 +5962,11 @@
       </c>
       <c r="S14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="3">
         <f t="shared" si="20"/>
@@ -6111,6 +6174,12 @@
       <c r="FH14" t="s">
         <v>136</v>
       </c>
+      <c r="FO14">
+        <v>22</v>
+      </c>
+      <c r="FP14" t="s">
+        <v>136</v>
+      </c>
       <c r="GY14">
         <v>90</v>
       </c>
@@ -6158,6 +6227,12 @@
       </c>
       <c r="HX14" t="s">
         <v>136</v>
+      </c>
+      <c r="KU14">
+        <v>90</v>
+      </c>
+      <c r="KV14" t="s">
+        <v>110</v>
       </c>
       <c r="PS14" s="3">
         <f t="shared" si="33"/>
@@ -6466,6 +6541,9 @@
       <c r="FH15" t="s">
         <v>136</v>
       </c>
+      <c r="FP15" t="s">
+        <v>139</v>
+      </c>
       <c r="GY15">
         <v>59</v>
       </c>
@@ -6519,11 +6597,11 @@
       </c>
       <c r="PS15" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="35"/>
@@ -7182,11 +7260,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1180</v>
+        <v>1225</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>546</v>
+        <v>591</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7202,7 +7280,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
@@ -7210,7 +7288,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="9"/>
@@ -7218,7 +7296,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
@@ -7226,7 +7304,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="13"/>
@@ -7266,11 +7344,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="23"/>
@@ -7282,7 +7360,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -7446,6 +7524,15 @@
       </c>
       <c r="FH18" t="s">
         <v>139</v>
+      </c>
+      <c r="FO18">
+        <v>45</v>
+      </c>
+      <c r="FP18" t="s">
+        <v>136</v>
+      </c>
+      <c r="FQ18">
+        <v>1</v>
       </c>
       <c r="GY18">
         <v>18</v>
@@ -7760,6 +7847,9 @@
       <c r="FH19" t="s">
         <v>138</v>
       </c>
+      <c r="FP19" t="s">
+        <v>139</v>
+      </c>
       <c r="GY19">
         <v>72</v>
       </c>
@@ -7819,11 +7909,11 @@
       </c>
       <c r="PS19" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="34"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="35"/>
@@ -7844,11 +7934,11 @@
       </c>
       <c r="B20">
         <f t="shared" si="37"/>
-        <v>1950</v>
+        <v>2018</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
-        <v>1287</v>
+        <v>1355</v>
       </c>
       <c r="D20">
         <f t="shared" si="3"/>
@@ -7864,11 +7954,11 @@
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="8"/>
@@ -7880,11 +7970,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="12"/>
@@ -8143,6 +8233,12 @@
         <v>82</v>
       </c>
       <c r="FH20" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO20">
+        <v>68</v>
+      </c>
+      <c r="FP20" t="s">
         <v>110</v>
       </c>
       <c r="GY20">
@@ -8464,11 +8560,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2457</v>
+        <v>2547</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1438</v>
+        <v>1528</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8484,11 +8580,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8500,11 +8596,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -8754,6 +8850,12 @@
         <v>89</v>
       </c>
       <c r="FH22" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO22">
+        <v>90</v>
+      </c>
+      <c r="FP22" t="s">
         <v>110</v>
       </c>
       <c r="GY22">
@@ -9089,7 +9191,7 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
@@ -9105,7 +9207,7 @@
       </c>
       <c r="N24" s="3">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <f t="shared" si="14"/>
@@ -9312,6 +9414,9 @@
       </c>
       <c r="FH24" t="s">
         <v>110</v>
+      </c>
+      <c r="FP24" t="s">
+        <v>138</v>
       </c>
       <c r="GY24">
         <v>90</v>
@@ -9677,7 +9782,7 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>971</v>
+        <v>1031</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -9689,7 +9794,7 @@
       </c>
       <c r="E26">
         <f t="shared" si="4"/>
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="F26">
         <f t="shared" si="5"/>
@@ -9697,11 +9802,11 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
@@ -9745,11 +9850,11 @@
       </c>
       <c r="S26">
         <f t="shared" si="18"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T26" s="3">
         <f t="shared" si="19"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26" s="3">
         <f t="shared" si="20"/>
@@ -9912,6 +10017,9 @@
       <c r="FH26" t="s">
         <v>139</v>
       </c>
+      <c r="FP26" t="s">
+        <v>139</v>
+      </c>
       <c r="GY26">
         <v>72</v>
       </c>
@@ -9981,13 +10089,19 @@
       <c r="KN26" t="s">
         <v>110</v>
       </c>
+      <c r="KU26">
+        <v>60</v>
+      </c>
+      <c r="KV26" t="s">
+        <v>110</v>
+      </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10008,11 +10122,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1477</v>
+        <v>1567</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>982</v>
+        <v>1072</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10028,11 +10142,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10044,11 +10158,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10220,6 +10334,12 @@
         <v>90</v>
       </c>
       <c r="FH27" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO27">
+        <v>90</v>
+      </c>
+      <c r="FP27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -10282,7 +10402,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="37"/>
-        <v>1385</v>
+        <v>1460</v>
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
@@ -10294,7 +10414,7 @@
       </c>
       <c r="E28">
         <f t="shared" si="4"/>
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="F28">
         <f t="shared" si="5"/>
@@ -10302,11 +10422,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="8"/>
@@ -10314,7 +10434,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <f t="shared" si="10"/>
@@ -10330,7 +10450,7 @@
       </c>
       <c r="N28" s="3">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28">
         <f t="shared" si="14"/>
@@ -10350,11 +10470,11 @@
       </c>
       <c r="S28">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" s="3">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" si="20"/>
@@ -10490,6 +10610,9 @@
       <c r="FH28" t="s">
         <v>139</v>
       </c>
+      <c r="FP28" t="s">
+        <v>138</v>
+      </c>
       <c r="GY28">
         <v>79</v>
       </c>
@@ -10548,6 +10671,12 @@
         <v>90</v>
       </c>
       <c r="KR28" t="s">
+        <v>110</v>
+      </c>
+      <c r="KU28">
+        <v>75</v>
+      </c>
+      <c r="KV28" t="s">
         <v>110</v>
       </c>
       <c r="PS28" s="3">
@@ -10577,11 +10706,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>669</v>
+        <v>737</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>429</v>
+        <v>497</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -10597,11 +10726,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -10613,11 +10742,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -10771,6 +10900,12 @@
         <v>90</v>
       </c>
       <c r="FH29" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO29">
+        <v>68</v>
+      </c>
+      <c r="FP29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -10830,11 +10965,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="67">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="68">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="69">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -10850,11 +10985,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="71">SUM(H30:I30)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="72">COUNTIF(AI30:PR30,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="73">COUNTIF(AI30:PR30,"R")</f>
@@ -10866,11 +11001,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="75">SUM(L30:M30)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="76">COUNTIF(CY30:GX30,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="77">COUNTIF(CY30:GX30,"R")</f>
@@ -10997,6 +11132,12 @@
         <v>72</v>
       </c>
       <c r="FH30" t="s">
+        <v>110</v>
+      </c>
+      <c r="FO30">
+        <v>45</v>
+      </c>
+      <c r="FP30" t="s">
         <v>110</v>
       </c>
       <c r="KI30">
@@ -11032,11 +11173,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11052,11 +11193,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11068,11 +11209,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11124,11 +11265,11 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ref="Z31" si="128">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
@@ -11136,7 +11277,7 @@
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31">
         <f t="shared" ref="AC31" si="131">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
@@ -11187,6 +11328,15 @@
         <v>110</v>
       </c>
       <c r="FI31">
+        <v>1</v>
+      </c>
+      <c r="FO31">
+        <v>90</v>
+      </c>
+      <c r="FP31" t="s">
+        <v>110</v>
+      </c>
+      <c r="FR31">
         <v>1</v>
       </c>
       <c r="PS31" s="3">
@@ -11216,11 +11366,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11228,7 +11378,7 @@
       </c>
       <c r="E32">
         <f t="shared" ref="E32" si="145">SUM(IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F32">
         <f t="shared" ref="F32" si="146">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32)</f>
@@ -11236,15 +11386,15 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -11252,7 +11402,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -11260,7 +11410,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -11284,11 +11434,11 @@
       </c>
       <c r="S32">
         <f t="shared" ref="S32" si="159">SUM(T32:U32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" s="3">
         <f t="shared" ref="T32" si="160">COUNTIF(IU32:PR32,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" s="3">
         <f t="shared" ref="U32" si="161">COUNTIF(IU32:PR32,"R")</f>
@@ -11308,11 +11458,11 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" ref="Y32" si="165">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32,DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="4">
         <f t="shared" ref="Z32" si="166">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32">
         <f t="shared" ref="AA32" si="167">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
@@ -11320,7 +11470,7 @@
       </c>
       <c r="AB32">
         <f t="shared" ref="AB32" si="168">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32">
         <f t="shared" ref="AC32" si="169">SUM(HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32)</f>
@@ -11364,10 +11514,25 @@
       <c r="FH32" t="s">
         <v>136</v>
       </c>
+      <c r="FO32">
+        <v>22</v>
+      </c>
+      <c r="FP32" t="s">
+        <v>136</v>
+      </c>
+      <c r="FR32">
+        <v>1</v>
+      </c>
       <c r="KQ32">
         <v>90</v>
       </c>
       <c r="KR32" t="s">
+        <v>110</v>
+      </c>
+      <c r="KU32">
+        <v>90</v>
+      </c>
+      <c r="KV32" t="s">
         <v>110</v>
       </c>
       <c r="PS32" s="3">

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5768A0A-4701-E549-83C2-96040370428D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14ECF7A-ABBB-A248-994B-FA265D8EAB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1635</v>
+        <v>1725</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1350</v>
+        <v>1440</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2551,6 +2551,12 @@
         <v>90</v>
       </c>
       <c r="FP2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS2">
+        <v>90</v>
+      </c>
+      <c r="FT2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2791,6 +2797,9 @@
       <c r="FP3" t="s">
         <v>139</v>
       </c>
+      <c r="FT3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2853,11 +2862,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2910,7 +2919,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2926,7 +2935,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3094,6 +3103,9 @@
       </c>
       <c r="FP4" t="s">
         <v>139</v>
+      </c>
+      <c r="FT4" t="s">
+        <v>138</v>
       </c>
       <c r="GY4">
         <v>90</v>
@@ -3188,11 +3200,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1383</v>
+        <v>1473</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>773</v>
+        <v>863</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3208,11 +3220,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3224,11 +3236,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3442,6 +3454,12 @@
         <v>90</v>
       </c>
       <c r="FP5" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS5">
+        <v>90</v>
+      </c>
+      <c r="FT5" t="s">
         <v>110</v>
       </c>
       <c r="HD5" t="s">
@@ -3718,6 +3736,9 @@
       <c r="FP6" t="s">
         <v>139</v>
       </c>
+      <c r="FT6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3750,11 +3771,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -4025,6 +4046,9 @@
       <c r="FQ7">
         <v>1</v>
       </c>
+      <c r="FT7" t="s">
+        <v>139</v>
+      </c>
       <c r="GY7">
         <v>90</v>
       </c>
@@ -4072,11 +4096,11 @@
       </c>
       <c r="PS7" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="34"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="35"/>
@@ -4314,6 +4338,9 @@
       <c r="FP8" t="s">
         <v>139</v>
       </c>
+      <c r="FT8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4391,11 +4418,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4416,11 +4443,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2047</v>
+        <v>2137</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1291</v>
+        <v>1381</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4436,11 +4463,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4452,11 +4479,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4685,6 +4712,12 @@
         <v>90</v>
       </c>
       <c r="FP9" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS9">
+        <v>90</v>
+      </c>
+      <c r="FT9" t="s">
         <v>110</v>
       </c>
       <c r="HC9">
@@ -4756,11 +4789,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1331</v>
+        <v>1421</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>731</v>
+        <v>821</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4776,11 +4809,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4792,11 +4825,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5004,6 +5037,12 @@
         <v>90</v>
       </c>
       <c r="FP10" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS10">
+        <v>90</v>
+      </c>
+      <c r="FT10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5316,6 +5355,9 @@
       <c r="FP11" t="s">
         <v>139</v>
       </c>
+      <c r="FT11" t="s">
+        <v>139</v>
+      </c>
       <c r="GY11">
         <v>90</v>
       </c>
@@ -5378,11 +5420,11 @@
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="33"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="34"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="35"/>
@@ -5849,6 +5891,9 @@
       <c r="FP13" t="s">
         <v>139</v>
       </c>
+      <c r="FT13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -5869,11 +5914,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -5926,7 +5971,7 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
@@ -5942,7 +5987,7 @@
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14">
         <f t="shared" si="14"/>
@@ -6179,6 +6224,9 @@
       </c>
       <c r="FP14" t="s">
         <v>136</v>
+      </c>
+      <c r="FT14" t="s">
+        <v>138</v>
       </c>
       <c r="GY14">
         <v>90</v>
@@ -6261,11 +6309,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1396</v>
+        <v>1415</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6281,7 +6329,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
@@ -6289,7 +6337,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="9"/>
@@ -6297,7 +6345,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
@@ -6305,7 +6353,7 @@
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="13"/>
@@ -6543,6 +6591,12 @@
       </c>
       <c r="FP15" t="s">
         <v>139</v>
+      </c>
+      <c r="FS15">
+        <v>19</v>
+      </c>
+      <c r="FT15" t="s">
+        <v>136</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7260,11 +7314,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1225</v>
+        <v>1305</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7280,11 +7334,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7296,11 +7350,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7533,6 +7587,12 @@
       </c>
       <c r="FQ18">
         <v>1</v>
+      </c>
+      <c r="FS18">
+        <v>80</v>
+      </c>
+      <c r="FT18" t="s">
+        <v>110</v>
       </c>
       <c r="GY18">
         <v>18</v>
@@ -7850,6 +7910,9 @@
       <c r="FP19" t="s">
         <v>139</v>
       </c>
+      <c r="FT19" t="s">
+        <v>139</v>
+      </c>
       <c r="GY19">
         <v>72</v>
       </c>
@@ -7909,11 +7972,11 @@
       </c>
       <c r="PS19" s="3">
         <f t="shared" si="33"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="34"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="35"/>
@@ -7934,11 +7997,11 @@
       </c>
       <c r="B20">
         <f t="shared" si="37"/>
-        <v>2018</v>
+        <v>2108</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
-        <v>1355</v>
+        <v>1445</v>
       </c>
       <c r="D20">
         <f t="shared" si="3"/>
@@ -7954,11 +8017,11 @@
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="8"/>
@@ -7970,11 +8033,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="12"/>
@@ -8239,6 +8302,12 @@
         <v>68</v>
       </c>
       <c r="FP20" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS20">
+        <v>90</v>
+      </c>
+      <c r="FT20" t="s">
         <v>110</v>
       </c>
       <c r="GY20">
@@ -8560,11 +8629,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2547</v>
+        <v>2637</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1528</v>
+        <v>1618</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8580,11 +8649,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8596,11 +8665,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -8856,6 +8925,12 @@
         <v>90</v>
       </c>
       <c r="FP22" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS22">
+        <v>90</v>
+      </c>
+      <c r="FT22" t="s">
         <v>110</v>
       </c>
       <c r="GY22">
@@ -9159,11 +9234,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>1997</v>
+        <v>2087</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1305</v>
+        <v>1395</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9179,11 +9254,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9195,11 +9270,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9417,6 +9492,12 @@
       </c>
       <c r="FP24" t="s">
         <v>138</v>
+      </c>
+      <c r="FS24">
+        <v>90</v>
+      </c>
+      <c r="FT24" t="s">
+        <v>110</v>
       </c>
       <c r="GY24">
         <v>90</v>
@@ -10020,6 +10101,9 @@
       <c r="FP26" t="s">
         <v>139</v>
       </c>
+      <c r="FT26" t="s">
+        <v>139</v>
+      </c>
       <c r="GY26">
         <v>72</v>
       </c>
@@ -10097,11 +10181,11 @@
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10122,11 +10206,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1567</v>
+        <v>1657</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1072</v>
+        <v>1162</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10142,11 +10226,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10158,11 +10242,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10340,6 +10424,12 @@
         <v>90</v>
       </c>
       <c r="FP27" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS27">
+        <v>90</v>
+      </c>
+      <c r="FT27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -10434,7 +10524,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28">
         <f t="shared" si="10"/>
@@ -10450,7 +10540,7 @@
       </c>
       <c r="N28" s="3">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28">
         <f t="shared" si="14"/>
@@ -10611,6 +10701,9 @@
         <v>139</v>
       </c>
       <c r="FP28" t="s">
+        <v>138</v>
+      </c>
+      <c r="FT28" t="s">
         <v>138</v>
       </c>
       <c r="GY28">
@@ -10706,11 +10799,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>737</v>
+        <v>808</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>497</v>
+        <v>568</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -10726,11 +10819,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -10742,11 +10835,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -10906,6 +10999,12 @@
         <v>68</v>
       </c>
       <c r="FP29" t="s">
+        <v>110</v>
+      </c>
+      <c r="FS29">
+        <v>71</v>
+      </c>
+      <c r="FT29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -10965,11 +11064,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="67">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="68">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="69">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -10985,7 +11084,7 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="71">SUM(H30:I30)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="72">COUNTIF(AI30:PR30,"T")</f>
@@ -10993,7 +11092,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="73">COUNTIF(AI30:PR30,"R")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="74">COUNTIF(AI30:PR30,"NR")</f>
@@ -11001,7 +11100,7 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="75">SUM(L30:M30)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="76">COUNTIF(CY30:GX30,"T")</f>
@@ -11009,7 +11108,7 @@
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="77">COUNTIF(CY30:GX30,"R")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" s="3">
         <f t="shared" ref="N30" si="78">COUNTIF(CY30:GX30,"NR")</f>
@@ -11139,6 +11238,12 @@
       </c>
       <c r="FP30" t="s">
         <v>110</v>
+      </c>
+      <c r="FS30">
+        <v>10</v>
+      </c>
+      <c r="FT30" t="s">
+        <v>136</v>
       </c>
       <c r="KI30">
         <v>90</v>
@@ -11173,11 +11278,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11193,11 +11298,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11209,11 +11314,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11338,6 +11443,12 @@
       </c>
       <c r="FR31">
         <v>1</v>
+      </c>
+      <c r="FS31">
+        <v>90</v>
+      </c>
+      <c r="FT31" t="s">
+        <v>110</v>
       </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
@@ -11523,6 +11634,9 @@
       <c r="FR32">
         <v>1</v>
       </c>
+      <c r="FT32" t="s">
+        <v>139</v>
+      </c>
       <c r="KQ32">
         <v>90</v>
       </c>
@@ -11537,11 +11651,11 @@
       </c>
       <c r="PS32" s="3">
         <f t="shared" ref="PS32" si="175">COUNTIF(AI32:PR32,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT32" s="3">
         <f t="shared" ref="PT32" si="176">COUNTIF(CY32:GX32,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU32" s="3">
         <f t="shared" ref="PU32" si="177">COUNTIF(GY32:IT32,"HG")</f>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14ECF7A-ABBB-A248-994B-FA265D8EAB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0470B2BC-61FE-1A47-BE96-009D304AF46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1725</v>
+        <v>1815</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1440</v>
+        <v>1530</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2557,6 +2557,12 @@
         <v>90</v>
       </c>
       <c r="FT2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW2">
+        <v>90</v>
+      </c>
+      <c r="FX2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2604,7 +2610,7 @@
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C29" si="2">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
@@ -2616,7 +2622,7 @@
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E29" si="4">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F30" si="5">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
@@ -2624,11 +2630,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G29" si="6">SUM(H3:I3)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H29" si="7">COUNTIF(AI3:PR3,"T")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I29" si="8">COUNTIF(AI3:PR3,"R")</f>
@@ -2672,11 +2678,11 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S29" si="18">SUM(T3:U3)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" ref="T3:T29" si="19">COUNTIF(IU3:PR3,"T")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" ref="U3:U29" si="20">COUNTIF(IU3:PR3,"R")</f>
@@ -2800,6 +2806,9 @@
       <c r="FT3" t="s">
         <v>139</v>
       </c>
+      <c r="FX3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2852,6 +2861,12 @@
         <v>90</v>
       </c>
       <c r="KR3" t="s">
+        <v>110</v>
+      </c>
+      <c r="KY3">
+        <v>90</v>
+      </c>
+      <c r="KZ3" t="s">
         <v>110</v>
       </c>
       <c r="ME3">
@@ -2862,11 +2877,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -3107,6 +3122,9 @@
       <c r="FT4" t="s">
         <v>138</v>
       </c>
+      <c r="FX4" t="s">
+        <v>139</v>
+      </c>
       <c r="GY4">
         <v>90</v>
       </c>
@@ -3175,11 +3193,11 @@
       </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="63">COUNTIF(AI4:PR4,"HG")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="64">COUNTIF(CY4:GX4,"HG")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="65">COUNTIF(GY4:IT4,"HG")</f>
@@ -3200,11 +3218,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1473</v>
+        <v>1563</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>863</v>
+        <v>953</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3220,11 +3238,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3236,11 +3254,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3284,11 +3302,11 @@
       </c>
       <c r="W5" s="3">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="23"/>
@@ -3300,7 +3318,7 @@
       </c>
       <c r="AA5">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5">
         <f t="shared" si="26"/>
@@ -3461,6 +3479,15 @@
       </c>
       <c r="FT5" t="s">
         <v>110</v>
+      </c>
+      <c r="FW5">
+        <v>90</v>
+      </c>
+      <c r="FX5" t="s">
+        <v>110</v>
+      </c>
+      <c r="FY5">
+        <v>1</v>
       </c>
       <c r="HD5" t="s">
         <v>139</v>
@@ -3516,7 +3543,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="37"/>
-        <v>450</v>
+        <v>516</v>
       </c>
       <c r="C6">
         <f t="shared" si="2"/>
@@ -3528,7 +3555,7 @@
       </c>
       <c r="E6">
         <f t="shared" si="4"/>
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="F6">
         <f t="shared" si="5"/>
@@ -3536,11 +3563,11 @@
       </c>
       <c r="G6">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="8"/>
@@ -3584,11 +3611,11 @@
       </c>
       <c r="S6">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="20"/>
@@ -3739,6 +3766,9 @@
       <c r="FT6" t="s">
         <v>139</v>
       </c>
+      <c r="FX6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3767,15 +3797,21 @@
         <v>90</v>
       </c>
       <c r="KF6" t="s">
+        <v>110</v>
+      </c>
+      <c r="KY6">
+        <v>66</v>
+      </c>
+      <c r="KZ6" t="s">
         <v>110</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3796,11 +3832,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>1938</v>
+        <v>2028</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1093</v>
+        <v>1183</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3816,11 +3852,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3832,11 +3868,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4048,6 +4084,12 @@
       </c>
       <c r="FT7" t="s">
         <v>139</v>
+      </c>
+      <c r="FW7">
+        <v>90</v>
+      </c>
+      <c r="FX7" t="s">
+        <v>110</v>
       </c>
       <c r="GY7">
         <v>90</v>
@@ -4341,6 +4383,9 @@
       <c r="FT8" t="s">
         <v>139</v>
       </c>
+      <c r="FX8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4418,11 +4463,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4443,11 +4488,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2137</v>
+        <v>2227</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1381</v>
+        <v>1471</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4463,11 +4508,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4479,11 +4524,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4535,11 +4580,11 @@
       </c>
       <c r="Y9" s="4">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" s="4">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA9">
         <f t="shared" si="25"/>
@@ -4547,7 +4592,7 @@
       </c>
       <c r="AB9">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9">
         <f t="shared" si="27"/>
@@ -4719,6 +4764,15 @@
       </c>
       <c r="FT9" t="s">
         <v>110</v>
+      </c>
+      <c r="FW9">
+        <v>90</v>
+      </c>
+      <c r="FX9" t="s">
+        <v>110</v>
+      </c>
+      <c r="FZ9">
+        <v>1</v>
       </c>
       <c r="HC9">
         <v>45</v>
@@ -5045,6 +5099,9 @@
       <c r="FT10" t="s">
         <v>110</v>
       </c>
+      <c r="FX10" t="s">
+        <v>139</v>
+      </c>
       <c r="HD10" t="s">
         <v>139</v>
       </c>
@@ -5092,11 +5149,11 @@
       </c>
       <c r="PS10" s="3">
         <f t="shared" si="33"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="PT10" s="3">
         <f t="shared" si="34"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU10" s="3">
         <f t="shared" si="35"/>
@@ -5117,11 +5174,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5137,7 +5194,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5145,7 +5202,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5153,7 +5210,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5161,7 +5218,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5357,6 +5414,12 @@
       </c>
       <c r="FT11" t="s">
         <v>139</v>
+      </c>
+      <c r="FW11">
+        <v>1</v>
+      </c>
+      <c r="FX11" t="s">
+        <v>136</v>
       </c>
       <c r="GY11">
         <v>90</v>
@@ -5894,6 +5957,9 @@
       <c r="FT13" t="s">
         <v>139</v>
       </c>
+      <c r="FX13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -5914,11 +5980,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -5939,7 +6005,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>1805</v>
+        <v>1895</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
@@ -5951,7 +6017,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="4"/>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F14">
         <f t="shared" si="5"/>
@@ -5959,11 +6025,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
@@ -5971,7 +6037,7 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
@@ -5987,7 +6053,7 @@
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14">
         <f t="shared" si="14"/>
@@ -6007,11 +6073,11 @@
       </c>
       <c r="S14">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="3">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" s="3">
         <f t="shared" si="20"/>
@@ -6228,6 +6294,9 @@
       <c r="FT14" t="s">
         <v>138</v>
       </c>
+      <c r="FX14" t="s">
+        <v>138</v>
+      </c>
       <c r="GY14">
         <v>90</v>
       </c>
@@ -6280,6 +6349,12 @@
         <v>90</v>
       </c>
       <c r="KV14" t="s">
+        <v>110</v>
+      </c>
+      <c r="KY14">
+        <v>90</v>
+      </c>
+      <c r="KZ14" t="s">
         <v>110</v>
       </c>
       <c r="PS14" s="3">
@@ -6309,11 +6384,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1415</v>
+        <v>1426</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6329,7 +6404,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
@@ -6337,7 +6412,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="9"/>
@@ -6345,7 +6420,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
@@ -6353,7 +6428,7 @@
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="13"/>
@@ -6401,11 +6476,11 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="4">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15">
         <f t="shared" si="25"/>
@@ -6413,7 +6488,7 @@
       </c>
       <c r="AB15">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15">
         <f t="shared" si="27"/>
@@ -6597,6 +6672,15 @@
       </c>
       <c r="FT15" t="s">
         <v>136</v>
+      </c>
+      <c r="FW15">
+        <v>11</v>
+      </c>
+      <c r="FX15" t="s">
+        <v>136</v>
+      </c>
+      <c r="FZ15">
+        <v>1</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7314,11 +7398,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1305</v>
+        <v>1384</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>671</v>
+        <v>750</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7334,11 +7418,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7350,11 +7434,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7592,6 +7676,12 @@
         <v>80</v>
       </c>
       <c r="FT18" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW18">
+        <v>79</v>
+      </c>
+      <c r="FX18" t="s">
         <v>110</v>
       </c>
       <c r="GY18">
@@ -7669,11 +7759,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1037</v>
+        <v>1138</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -7681,7 +7771,7 @@
       </c>
       <c r="E19">
         <f t="shared" si="4"/>
-        <v>242</v>
+        <v>332</v>
       </c>
       <c r="F19">
         <f t="shared" si="5"/>
@@ -7689,15 +7779,15 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="9"/>
@@ -7705,7 +7795,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
@@ -7713,7 +7803,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="13"/>
@@ -7737,11 +7827,11 @@
       </c>
       <c r="S19">
         <f>SUM(T19:U19)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="20"/>
@@ -7913,6 +8003,12 @@
       <c r="FT19" t="s">
         <v>139</v>
       </c>
+      <c r="FW19">
+        <v>11</v>
+      </c>
+      <c r="FX19" t="s">
+        <v>136</v>
+      </c>
       <c r="GY19">
         <v>72</v>
       </c>
@@ -7968,6 +8064,12 @@
         <v>62</v>
       </c>
       <c r="KR19" t="s">
+        <v>110</v>
+      </c>
+      <c r="KY19">
+        <v>90</v>
+      </c>
+      <c r="KZ19" t="s">
         <v>110</v>
       </c>
       <c r="PS19" s="3">
@@ -7997,11 +8099,11 @@
       </c>
       <c r="B20">
         <f t="shared" si="37"/>
-        <v>2108</v>
+        <v>2187</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
-        <v>1445</v>
+        <v>1524</v>
       </c>
       <c r="D20">
         <f t="shared" si="3"/>
@@ -8017,11 +8119,11 @@
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="8"/>
@@ -8033,11 +8135,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M20" s="3">
         <f t="shared" si="12"/>
@@ -8308,6 +8410,12 @@
         <v>90</v>
       </c>
       <c r="FT20" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW20">
+        <v>79</v>
+      </c>
+      <c r="FX20" t="s">
         <v>110</v>
       </c>
       <c r="GY20">
@@ -8629,11 +8737,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2637</v>
+        <v>2726</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1618</v>
+        <v>1707</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8649,11 +8757,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8665,11 +8773,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -8931,6 +9039,12 @@
         <v>90</v>
       </c>
       <c r="FT22" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW22">
+        <v>89</v>
+      </c>
+      <c r="FX22" t="s">
         <v>110</v>
       </c>
       <c r="GY22">
@@ -9234,11 +9348,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2087</v>
+        <v>2177</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1395</v>
+        <v>1485</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9254,11 +9368,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9270,11 +9384,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9497,6 +9611,12 @@
         <v>90</v>
       </c>
       <c r="FT24" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW24">
+        <v>90</v>
+      </c>
+      <c r="FX24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10104,6 +10224,9 @@
       <c r="FT26" t="s">
         <v>139</v>
       </c>
+      <c r="FX26" t="s">
+        <v>139</v>
+      </c>
       <c r="GY26">
         <v>72</v>
       </c>
@@ -10181,11 +10304,11 @@
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10206,11 +10329,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1657</v>
+        <v>1747</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1162</v>
+        <v>1252</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10226,11 +10349,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10242,11 +10365,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10430,6 +10553,12 @@
         <v>90</v>
       </c>
       <c r="FT27" t="s">
+        <v>110</v>
+      </c>
+      <c r="FW27">
+        <v>90</v>
+      </c>
+      <c r="FX27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -10492,7 +10621,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="37"/>
-        <v>1460</v>
+        <v>1550</v>
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
@@ -10504,7 +10633,7 @@
       </c>
       <c r="E28">
         <f t="shared" si="4"/>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="F28">
         <f t="shared" si="5"/>
@@ -10512,11 +10641,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="8"/>
@@ -10560,11 +10689,11 @@
       </c>
       <c r="S28">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" s="3">
         <f t="shared" si="19"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" si="20"/>
@@ -10706,6 +10835,9 @@
       <c r="FT28" t="s">
         <v>138</v>
       </c>
+      <c r="FX28" t="s">
+        <v>139</v>
+      </c>
       <c r="GY28">
         <v>79</v>
       </c>
@@ -10772,13 +10904,19 @@
       <c r="KV28" t="s">
         <v>110</v>
       </c>
+      <c r="KY28">
+        <v>90</v>
+      </c>
+      <c r="KZ28" t="s">
+        <v>110</v>
+      </c>
       <c r="PS28" s="3">
         <f t="shared" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PT28" s="3">
         <f t="shared" si="34"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU28" s="3">
         <f t="shared" si="35"/>
@@ -10799,11 +10937,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>808</v>
+        <v>898</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>568</v>
+        <v>658</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -10819,11 +10957,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -10835,11 +10973,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -10883,11 +11021,11 @@
       </c>
       <c r="W29" s="3">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="4">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="23"/>
@@ -10899,7 +11037,7 @@
       </c>
       <c r="AA29">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29">
         <f t="shared" si="26"/>
@@ -11006,6 +11144,15 @@
       </c>
       <c r="FT29" t="s">
         <v>110</v>
+      </c>
+      <c r="FW29">
+        <v>90</v>
+      </c>
+      <c r="FX29" t="s">
+        <v>110</v>
+      </c>
+      <c r="FY29">
+        <v>1</v>
       </c>
       <c r="HC29">
         <v>90</v>
@@ -11064,11 +11211,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="67">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="68">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="69">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -11084,11 +11231,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="71">SUM(H30:I30)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="72">COUNTIF(AI30:PR30,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="73">COUNTIF(AI30:PR30,"R")</f>
@@ -11100,11 +11247,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="75">SUM(L30:M30)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="76">COUNTIF(CY30:GX30,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="77">COUNTIF(CY30:GX30,"R")</f>
@@ -11244,6 +11391,12 @@
       </c>
       <c r="FT30" t="s">
         <v>136</v>
+      </c>
+      <c r="FW30">
+        <v>63</v>
+      </c>
+      <c r="FX30" t="s">
+        <v>110</v>
       </c>
       <c r="KI30">
         <v>90</v>
@@ -11450,13 +11603,16 @@
       <c r="FT31" t="s">
         <v>110</v>
       </c>
+      <c r="FX31" t="s">
+        <v>139</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="138">COUNTIF(CY31:GX31,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="139">COUNTIF(GY31:IT31,"HG")</f>
@@ -11477,11 +11633,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11497,7 +11653,7 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
@@ -11505,7 +11661,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -11513,7 +11669,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -11521,7 +11677,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -11561,27 +11717,27 @@
       </c>
       <c r="W32" s="3">
         <f t="shared" ref="W32" si="163">SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32,DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MG32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="4">
         <f t="shared" ref="X32" si="164">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MG32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="4">
         <f t="shared" ref="Y32" si="165">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32,DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="4">
         <f t="shared" ref="Z32" si="166">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA32">
         <f t="shared" ref="AA32" si="167">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32">
         <f t="shared" ref="AB32" si="168">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <f t="shared" ref="AC32" si="169">SUM(HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32)</f>
@@ -11636,6 +11792,18 @@
       </c>
       <c r="FT32" t="s">
         <v>139</v>
+      </c>
+      <c r="FW32">
+        <v>27</v>
+      </c>
+      <c r="FX32" t="s">
+        <v>136</v>
+      </c>
+      <c r="FY32">
+        <v>1</v>
+      </c>
+      <c r="FZ32">
+        <v>1</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0470B2BC-61FE-1A47-BE96-009D304AF46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D587FA-7E60-8E46-BFA3-69DA831665E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1815</v>
+        <v>1905</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1530</v>
+        <v>1620</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2563,6 +2563,12 @@
         <v>90</v>
       </c>
       <c r="FX2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA2">
+        <v>90</v>
+      </c>
+      <c r="GB2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2809,6 +2815,9 @@
       <c r="FX3" t="s">
         <v>139</v>
       </c>
+      <c r="GB3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2877,11 +2886,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2902,7 +2911,7 @@
       </c>
       <c r="B4">
         <f t="shared" ref="B4:B29" si="37">SUM(AI4,AM4,AQ4,AU4,AY4,BC4,BG4,BK4,BO4,BS4,BW4,CA4,CE4,CI4,CM4,CQ4,CU4,CY4,DC4,DG4,DK4,DO4,DS4,DW4,EA4,EE4,EI4,EM4,EQ4,EU4,EY4,FC4,FG4,FK4,FO4,FS4,FW4,GA4,GE4,GI4,GM4,GQ4,GU4,GY4,HC4,HG4,HK4,HO4,HS4,HW4,IA4,IE4,II4,IM4,IQ4,IU4,IY4,JC4,JG4,JK4,JO4,JS4,JW4,KA4,KE4,KI4,KM4,KQ4,KU4,KY4,LC4,LG4,LK4,LO4,LS4,LW4,MA4,ME4,MI4,MM4,MQ4,MU4,MY4,NC4,NG4,NK4,NO4,NS4,NW4,OA4,OE4,OI4,OM4,OQ4,OU4,OY4,PC4,PG4,PK4,PO4)</f>
-        <v>1425</v>
+        <v>1515</v>
       </c>
       <c r="C4">
         <f t="shared" si="2"/>
@@ -2914,7 +2923,7 @@
       </c>
       <c r="E4">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="F4">
         <f t="shared" si="5"/>
@@ -2922,11 +2931,11 @@
       </c>
       <c r="G4">
         <f t="shared" ref="G4" si="38">SUM(H4:I4)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="39">COUNTIF(AI4:PR4,"T")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="40">COUNTIF(AI4:PR4,"R")</f>
@@ -2934,7 +2943,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2950,7 +2959,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -2970,11 +2979,11 @@
       </c>
       <c r="S4">
         <f t="shared" ref="S4" si="50">SUM(T4:U4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3">
         <f t="shared" si="19"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" s="3">
         <f t="shared" si="20"/>
@@ -3125,6 +3134,9 @@
       <c r="FX4" t="s">
         <v>139</v>
       </c>
+      <c r="GB4" t="s">
+        <v>138</v>
+      </c>
       <c r="GY4">
         <v>90</v>
       </c>
@@ -3189,6 +3201,12 @@
         <v>90</v>
       </c>
       <c r="KV4" t="s">
+        <v>110</v>
+      </c>
+      <c r="LC4">
+        <v>90</v>
+      </c>
+      <c r="LD4" t="s">
         <v>110</v>
       </c>
       <c r="PS4" s="3">
@@ -3218,11 +3236,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1563</v>
+        <v>1571</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3238,7 +3256,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
@@ -3246,7 +3264,7 @@
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="9"/>
@@ -3254,7 +3272,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
@@ -3262,7 +3280,7 @@
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="13"/>
@@ -3488,6 +3506,12 @@
       </c>
       <c r="FY5">
         <v>1</v>
+      </c>
+      <c r="GA5">
+        <v>8</v>
+      </c>
+      <c r="GB5" t="s">
+        <v>136</v>
       </c>
       <c r="HD5" t="s">
         <v>139</v>
@@ -3543,7 +3567,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="37"/>
-        <v>516</v>
+        <v>606</v>
       </c>
       <c r="C6">
         <f t="shared" si="2"/>
@@ -3555,7 +3579,7 @@
       </c>
       <c r="E6">
         <f t="shared" si="4"/>
-        <v>246</v>
+        <v>336</v>
       </c>
       <c r="F6">
         <f t="shared" si="5"/>
@@ -3563,11 +3587,11 @@
       </c>
       <c r="G6">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="8"/>
@@ -3611,11 +3635,11 @@
       </c>
       <c r="S6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" s="3">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="20"/>
@@ -3769,6 +3793,9 @@
       <c r="FX6" t="s">
         <v>139</v>
       </c>
+      <c r="GB6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3805,13 +3832,19 @@
       <c r="KZ6" t="s">
         <v>110</v>
       </c>
+      <c r="LC6">
+        <v>90</v>
+      </c>
+      <c r="LD6" t="s">
+        <v>110</v>
+      </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3832,11 +3865,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2028</v>
+        <v>2118</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1183</v>
+        <v>1273</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3852,11 +3885,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3868,11 +3901,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4089,6 +4122,12 @@
         <v>90</v>
       </c>
       <c r="FX7" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA7">
+        <v>90</v>
+      </c>
+      <c r="GB7" t="s">
         <v>110</v>
       </c>
       <c r="GY7">
@@ -4386,6 +4425,9 @@
       <c r="FX8" t="s">
         <v>139</v>
       </c>
+      <c r="GB8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4463,11 +4505,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4488,11 +4530,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2227</v>
+        <v>2317</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1471</v>
+        <v>1561</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4508,11 +4550,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4524,11 +4566,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4773,6 +4815,12 @@
       </c>
       <c r="FZ9">
         <v>1</v>
+      </c>
+      <c r="GA9">
+        <v>90</v>
+      </c>
+      <c r="GB9" t="s">
+        <v>110</v>
       </c>
       <c r="HC9">
         <v>45</v>
@@ -4843,11 +4891,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1421</v>
+        <v>1511</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>821</v>
+        <v>911</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4863,11 +4911,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4879,11 +4927,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5101,6 +5149,12 @@
       </c>
       <c r="FX10" t="s">
         <v>139</v>
+      </c>
+      <c r="GA10">
+        <v>90</v>
+      </c>
+      <c r="GB10" t="s">
+        <v>110</v>
       </c>
       <c r="HD10" t="s">
         <v>139</v>
@@ -5174,7 +5228,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1215</v>
+        <v>1229</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
@@ -5186,7 +5240,7 @@
       </c>
       <c r="E11">
         <f t="shared" si="4"/>
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="F11">
         <f t="shared" si="5"/>
@@ -5194,11 +5248,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
@@ -5242,11 +5296,11 @@
       </c>
       <c r="S11">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" s="3">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" si="20"/>
@@ -5421,6 +5475,9 @@
       <c r="FX11" t="s">
         <v>136</v>
       </c>
+      <c r="GB11" t="s">
+        <v>139</v>
+      </c>
       <c r="GY11">
         <v>90</v>
       </c>
@@ -5481,13 +5538,19 @@
       <c r="KV11" t="s">
         <v>110</v>
       </c>
+      <c r="LC11">
+        <v>14</v>
+      </c>
+      <c r="LD11" t="s">
+        <v>110</v>
+      </c>
       <c r="PS11" s="3">
         <f t="shared" si="33"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="34"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="35"/>
@@ -5960,6 +6023,9 @@
       <c r="FX13" t="s">
         <v>139</v>
       </c>
+      <c r="GB13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -5980,11 +6046,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6005,11 +6071,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>1895</v>
+        <v>1993</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6017,7 +6083,7 @@
       </c>
       <c r="E14">
         <f t="shared" si="4"/>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="F14">
         <f t="shared" si="5"/>
@@ -6025,15 +6091,15 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
@@ -6041,7 +6107,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
@@ -6049,7 +6115,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
@@ -6073,11 +6139,11 @@
       </c>
       <c r="S14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <f t="shared" si="20"/>
@@ -6297,6 +6363,12 @@
       <c r="FX14" t="s">
         <v>138</v>
       </c>
+      <c r="GA14">
+        <v>8</v>
+      </c>
+      <c r="GB14" t="s">
+        <v>136</v>
+      </c>
       <c r="GY14">
         <v>90</v>
       </c>
@@ -6355,6 +6427,12 @@
         <v>90</v>
       </c>
       <c r="KZ14" t="s">
+        <v>110</v>
+      </c>
+      <c r="LC14">
+        <v>90</v>
+      </c>
+      <c r="LD14" t="s">
         <v>110</v>
       </c>
       <c r="PS14" s="3">
@@ -6384,11 +6462,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1426</v>
+        <v>1442</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6404,7 +6482,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
@@ -6412,7 +6490,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="9"/>
@@ -6420,7 +6498,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
@@ -6428,7 +6506,7 @@
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="13"/>
@@ -6681,6 +6759,12 @@
       </c>
       <c r="FZ15">
         <v>1</v>
+      </c>
+      <c r="GA15">
+        <v>16</v>
+      </c>
+      <c r="GB15" t="s">
+        <v>136</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7398,11 +7482,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1384</v>
+        <v>1458</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>824</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7418,11 +7502,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7434,11 +7518,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7682,6 +7766,12 @@
         <v>79</v>
       </c>
       <c r="FX18" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA18">
+        <v>74</v>
+      </c>
+      <c r="GB18" t="s">
         <v>110</v>
       </c>
       <c r="GY18">
@@ -8009,6 +8099,9 @@
       <c r="FX19" t="s">
         <v>136</v>
       </c>
+      <c r="GB19" t="s">
+        <v>139</v>
+      </c>
       <c r="GY19">
         <v>72</v>
       </c>
@@ -8074,11 +8167,11 @@
       </c>
       <c r="PS19" s="3">
         <f t="shared" si="33"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="34"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="35"/>
@@ -8099,11 +8192,11 @@
       </c>
       <c r="B20">
         <f t="shared" si="37"/>
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="D20">
         <f t="shared" si="3"/>
@@ -8119,7 +8212,7 @@
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="7"/>
@@ -8127,7 +8220,7 @@
       </c>
       <c r="I20" s="3">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="9"/>
@@ -8135,7 +8228,7 @@
       </c>
       <c r="K20">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="11"/>
@@ -8143,7 +8236,7 @@
       </c>
       <c r="M20" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="3">
         <f t="shared" si="13"/>
@@ -8417,6 +8510,12 @@
       </c>
       <c r="FX20" t="s">
         <v>110</v>
+      </c>
+      <c r="GA20">
+        <v>10</v>
+      </c>
+      <c r="GB20" t="s">
+        <v>136</v>
       </c>
       <c r="GY20">
         <v>31</v>
@@ -8737,11 +8836,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2726</v>
+        <v>2808</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1707</v>
+        <v>1789</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8757,11 +8856,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8773,11 +8872,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -9045,6 +9144,12 @@
         <v>89</v>
       </c>
       <c r="FX22" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA22">
+        <v>82</v>
+      </c>
+      <c r="GB22" t="s">
         <v>110</v>
       </c>
       <c r="GY22">
@@ -9348,11 +9453,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2177</v>
+        <v>2267</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1575</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9368,11 +9473,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9384,11 +9489,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9617,6 +9722,12 @@
         <v>90</v>
       </c>
       <c r="FX24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA24">
+        <v>90</v>
+      </c>
+      <c r="GB24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -9983,7 +10094,7 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>1031</v>
+        <v>1100</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -9995,7 +10106,7 @@
       </c>
       <c r="E26">
         <f t="shared" si="4"/>
-        <v>580</v>
+        <v>649</v>
       </c>
       <c r="F26">
         <f t="shared" si="5"/>
@@ -10003,11 +10114,11 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
@@ -10051,11 +10162,11 @@
       </c>
       <c r="S26">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" s="3">
         <f t="shared" si="19"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26" s="3">
         <f t="shared" si="20"/>
@@ -10227,6 +10338,9 @@
       <c r="FX26" t="s">
         <v>139</v>
       </c>
+      <c r="GB26" t="s">
+        <v>139</v>
+      </c>
       <c r="GY26">
         <v>72</v>
       </c>
@@ -10302,13 +10416,19 @@
       <c r="KV26" t="s">
         <v>110</v>
       </c>
+      <c r="LC26">
+        <v>69</v>
+      </c>
+      <c r="LD26" t="s">
+        <v>110</v>
+      </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10329,11 +10449,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1747</v>
+        <v>1837</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1252</v>
+        <v>1342</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10349,11 +10469,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10365,11 +10485,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10559,6 +10679,12 @@
         <v>90</v>
       </c>
       <c r="FX27" t="s">
+        <v>110</v>
+      </c>
+      <c r="GA27">
+        <v>90</v>
+      </c>
+      <c r="GB27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -10937,11 +11063,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>898</v>
+        <v>980</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>658</v>
+        <v>740</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -10957,11 +11083,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -10973,11 +11099,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11153,6 +11279,12 @@
       </c>
       <c r="FY29">
         <v>1</v>
+      </c>
+      <c r="GA29">
+        <v>82</v>
+      </c>
+      <c r="GB29" t="s">
+        <v>110</v>
       </c>
       <c r="HC29">
         <v>90</v>
@@ -11211,7 +11343,7 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="67">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>479</v>
+        <v>569</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="68">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
@@ -11223,7 +11355,7 @@
       </c>
       <c r="E30">
         <f t="shared" ref="E30" si="70">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="F30">
         <f t="shared" si="5"/>
@@ -11231,11 +11363,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="71">SUM(H30:I30)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="72">COUNTIF(AI30:PR30,"T")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="73">COUNTIF(AI30:PR30,"R")</f>
@@ -11279,11 +11411,11 @@
       </c>
       <c r="S30">
         <f t="shared" ref="S30" si="83">SUM(T30:U30)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" s="3">
         <f t="shared" ref="T30" si="84">COUNTIF(IU30:PR30,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" s="3">
         <f t="shared" ref="U30" si="85">COUNTIF(IU30:PR30,"R")</f>
@@ -11398,19 +11530,28 @@
       <c r="FX30" t="s">
         <v>110</v>
       </c>
+      <c r="GB30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
       <c r="KJ30" t="s">
+        <v>110</v>
+      </c>
+      <c r="LC30">
+        <v>90</v>
+      </c>
+      <c r="LD30" t="s">
         <v>110</v>
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -11431,11 +11572,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11451,11 +11592,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11467,11 +11608,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11605,6 +11746,12 @@
       </c>
       <c r="FX31" t="s">
         <v>139</v>
+      </c>
+      <c r="GA31">
+        <v>90</v>
+      </c>
+      <c r="GB31" t="s">
+        <v>110</v>
       </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
@@ -11633,11 +11780,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11653,11 +11800,11 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
@@ -11669,11 +11816,11 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
@@ -11804,6 +11951,12 @@
       </c>
       <c r="FZ32">
         <v>1</v>
+      </c>
+      <c r="GA32">
+        <v>80</v>
+      </c>
+      <c r="GB32" t="s">
+        <v>110</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D587FA-7E60-8E46-BFA3-69DA831665E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716128F5-0ED6-A944-B1D6-994B7EB77C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1905</v>
+        <v>1995</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1620</v>
+        <v>1710</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2545,6 +2545,12 @@
         <v>90</v>
       </c>
       <c r="FH2" t="s">
+        <v>110</v>
+      </c>
+      <c r="FK2">
+        <v>90</v>
+      </c>
+      <c r="FL2" t="s">
         <v>110</v>
       </c>
       <c r="FO2">
@@ -2806,6 +2812,9 @@
       <c r="FH3" t="s">
         <v>139</v>
       </c>
+      <c r="FL3" t="s">
+        <v>139</v>
+      </c>
       <c r="FP3" t="s">
         <v>139</v>
       </c>
@@ -2886,11 +2895,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2943,7 +2952,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2959,7 +2968,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3124,6 +3133,9 @@
       </c>
       <c r="FH4" t="s">
         <v>139</v>
+      </c>
+      <c r="FL4" t="s">
+        <v>138</v>
       </c>
       <c r="FP4" t="s">
         <v>139</v>
@@ -3236,11 +3248,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1571</v>
+        <v>1661</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>961</v>
+        <v>1051</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3256,11 +3268,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3272,11 +3284,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3485,6 +3497,12 @@
       </c>
       <c r="FH5" t="s">
         <v>136</v>
+      </c>
+      <c r="FK5">
+        <v>90</v>
+      </c>
+      <c r="FL5" t="s">
+        <v>110</v>
       </c>
       <c r="FO5">
         <v>90</v>
@@ -3784,6 +3802,9 @@
       <c r="FH6" t="s">
         <v>139</v>
       </c>
+      <c r="FL6" t="s">
+        <v>139</v>
+      </c>
       <c r="FP6" t="s">
         <v>139</v>
       </c>
@@ -3840,11 +3861,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3865,11 +3886,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2118</v>
+        <v>2208</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1273</v>
+        <v>1363</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3885,11 +3906,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3901,11 +3922,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4104,6 +4125,12 @@
         <v>90</v>
       </c>
       <c r="FH7" t="s">
+        <v>110</v>
+      </c>
+      <c r="FK7">
+        <v>90</v>
+      </c>
+      <c r="FL7" t="s">
         <v>110</v>
       </c>
       <c r="FO7">
@@ -4416,6 +4443,9 @@
       <c r="FH8" t="s">
         <v>139</v>
       </c>
+      <c r="FL8" t="s">
+        <v>139</v>
+      </c>
       <c r="FP8" t="s">
         <v>139</v>
       </c>
@@ -4505,11 +4535,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4530,11 +4560,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2317</v>
+        <v>2407</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1561</v>
+        <v>1651</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4550,11 +4580,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4566,11 +4596,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4793,6 +4823,12 @@
         <v>90</v>
       </c>
       <c r="FH9" t="s">
+        <v>110</v>
+      </c>
+      <c r="FK9">
+        <v>90</v>
+      </c>
+      <c r="FL9" t="s">
         <v>110</v>
       </c>
       <c r="FO9">
@@ -4891,11 +4927,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1511</v>
+        <v>1601</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>911</v>
+        <v>1001</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4911,11 +4947,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4927,11 +4963,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -4983,11 +5019,11 @@
       </c>
       <c r="Y10" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10">
         <f t="shared" si="25"/>
@@ -4995,7 +5031,7 @@
       </c>
       <c r="AB10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10">
         <f t="shared" si="27"/>
@@ -5134,6 +5170,15 @@
       </c>
       <c r="FH10" t="s">
         <v>110</v>
+      </c>
+      <c r="FK10">
+        <v>90</v>
+      </c>
+      <c r="FL10" t="s">
+        <v>110</v>
+      </c>
+      <c r="FN10">
+        <v>1</v>
       </c>
       <c r="FO10">
         <v>90</v>
@@ -5463,6 +5508,9 @@
       <c r="FH11" t="s">
         <v>139</v>
       </c>
+      <c r="FL11" t="s">
+        <v>139</v>
+      </c>
       <c r="FP11" t="s">
         <v>139</v>
       </c>
@@ -5546,11 +5594,11 @@
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="33"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="PT11" s="3">
         <f t="shared" si="34"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="PU11" s="3">
         <f t="shared" si="35"/>
@@ -6014,6 +6062,9 @@
       <c r="FH13" t="s">
         <v>139</v>
       </c>
+      <c r="FL13" t="s">
+        <v>139</v>
+      </c>
       <c r="FP13" t="s">
         <v>139</v>
       </c>
@@ -6046,11 +6097,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6071,11 +6122,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>1993</v>
+        <v>2031</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>895</v>
+        <v>933</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6091,7 +6142,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
@@ -6099,7 +6150,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
@@ -6107,7 +6158,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
@@ -6115,7 +6166,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
@@ -6349,6 +6400,12 @@
         <v>18</v>
       </c>
       <c r="FH14" t="s">
+        <v>136</v>
+      </c>
+      <c r="FK14">
+        <v>38</v>
+      </c>
+      <c r="FL14" t="s">
         <v>136</v>
       </c>
       <c r="FO14">
@@ -6462,11 +6519,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1442</v>
+        <v>1487</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>705</v>
+        <v>750</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6482,11 +6539,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6498,11 +6555,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
@@ -6741,6 +6798,12 @@
       </c>
       <c r="FH15" t="s">
         <v>136</v>
+      </c>
+      <c r="FK15">
+        <v>45</v>
+      </c>
+      <c r="FL15" t="s">
+        <v>110</v>
       </c>
       <c r="FP15" t="s">
         <v>139</v>
@@ -7482,11 +7545,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1458</v>
+        <v>1503</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>824</v>
+        <v>869</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7502,7 +7565,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
@@ -7510,7 +7573,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="9"/>
@@ -7518,7 +7581,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
@@ -7526,7 +7589,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="13"/>
@@ -7566,11 +7629,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="23"/>
@@ -7582,7 +7645,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -7746,6 +7809,15 @@
       </c>
       <c r="FH18" t="s">
         <v>139</v>
+      </c>
+      <c r="FK18">
+        <v>45</v>
+      </c>
+      <c r="FL18" t="s">
+        <v>136</v>
+      </c>
+      <c r="FM18">
+        <v>1</v>
       </c>
       <c r="FO18">
         <v>45</v>
@@ -7849,11 +7921,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1138</v>
+        <v>1183</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -7869,7 +7941,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
@@ -7877,7 +7949,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="9"/>
@@ -7885,7 +7957,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
@@ -7893,7 +7965,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="13"/>
@@ -8086,6 +8158,12 @@
       </c>
       <c r="FH19" t="s">
         <v>138</v>
+      </c>
+      <c r="FK19">
+        <v>45</v>
+      </c>
+      <c r="FL19" t="s">
+        <v>136</v>
       </c>
       <c r="FP19" t="s">
         <v>139</v>
@@ -8493,6 +8571,9 @@
       <c r="FH20" t="s">
         <v>110</v>
       </c>
+      <c r="FL20" t="s">
+        <v>139</v>
+      </c>
       <c r="FO20">
         <v>68</v>
       </c>
@@ -8573,11 +8654,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -8836,11 +8917,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2808</v>
+        <v>2851</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1789</v>
+        <v>1832</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -8856,11 +8937,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -8872,11 +8953,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -9126,6 +9207,12 @@
         <v>89</v>
       </c>
       <c r="FH22" t="s">
+        <v>110</v>
+      </c>
+      <c r="FK22">
+        <v>43</v>
+      </c>
+      <c r="FL22" t="s">
         <v>110</v>
       </c>
       <c r="FO22">
@@ -9709,6 +9796,9 @@
       <c r="FH24" t="s">
         <v>110</v>
       </c>
+      <c r="FL24" t="s">
+        <v>139</v>
+      </c>
       <c r="FP24" t="s">
         <v>138</v>
       </c>
@@ -9771,11 +9861,11 @@
       </c>
       <c r="PS24" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="35"/>
@@ -10329,6 +10419,9 @@
       <c r="FH26" t="s">
         <v>139</v>
       </c>
+      <c r="FL26" t="s">
+        <v>139</v>
+      </c>
       <c r="FP26" t="s">
         <v>139</v>
       </c>
@@ -10424,11 +10517,11 @@
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10449,11 +10542,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1837</v>
+        <v>1927</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1342</v>
+        <v>1432</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10469,11 +10562,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10485,11 +10578,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -10541,11 +10634,11 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="4">
         <f t="shared" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA27">
         <f t="shared" si="25"/>
@@ -10553,7 +10646,7 @@
       </c>
       <c r="AB27">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC27">
         <f t="shared" si="27"/>
@@ -10662,6 +10755,15 @@
       </c>
       <c r="FH27" t="s">
         <v>110</v>
+      </c>
+      <c r="FK27">
+        <v>90</v>
+      </c>
+      <c r="FL27" t="s">
+        <v>110</v>
+      </c>
+      <c r="FN27">
+        <v>1</v>
       </c>
       <c r="FO27">
         <v>90</v>
@@ -11063,11 +11165,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>980</v>
+        <v>1032</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>740</v>
+        <v>792</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11083,11 +11185,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11099,11 +11201,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11257,6 +11359,12 @@
         <v>90</v>
       </c>
       <c r="FH29" t="s">
+        <v>110</v>
+      </c>
+      <c r="FK29">
+        <v>52</v>
+      </c>
+      <c r="FL29" t="s">
         <v>110</v>
       </c>
       <c r="FO29">
@@ -11512,6 +11620,9 @@
       <c r="FH30" t="s">
         <v>110</v>
       </c>
+      <c r="FL30" t="s">
+        <v>139</v>
+      </c>
       <c r="FO30">
         <v>45</v>
       </c>
@@ -11547,11 +11658,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -11572,11 +11683,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11592,11 +11703,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11608,11 +11719,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11656,11 +11767,11 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
@@ -11672,7 +11783,7 @@
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
@@ -11727,6 +11838,15 @@
         <v>110</v>
       </c>
       <c r="FI31">
+        <v>1</v>
+      </c>
+      <c r="FK31">
+        <v>90</v>
+      </c>
+      <c r="FL31" t="s">
+        <v>110</v>
+      </c>
+      <c r="FM31">
         <v>1</v>
       </c>
       <c r="FO31">
@@ -11780,11 +11900,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11800,11 +11920,11 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
@@ -11816,11 +11936,11 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
@@ -11927,6 +12047,12 @@
       </c>
       <c r="FH32" t="s">
         <v>136</v>
+      </c>
+      <c r="FK32">
+        <v>45</v>
+      </c>
+      <c r="FL32" t="s">
+        <v>110</v>
       </c>
       <c r="FO32">
         <v>22</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716128F5-0ED6-A944-B1D6-994B7EB77C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A09E1E-FA33-C34D-971F-A901BAFB4D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>1995</v>
+        <v>2085</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1710</v>
+        <v>1800</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2575,6 +2575,12 @@
         <v>90</v>
       </c>
       <c r="GB2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE2">
+        <v>90</v>
+      </c>
+      <c r="GF2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2827,6 +2833,9 @@
       <c r="GB3" t="s">
         <v>139</v>
       </c>
+      <c r="GF3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2895,11 +2904,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -3149,6 +3158,9 @@
       <c r="GB4" t="s">
         <v>138</v>
       </c>
+      <c r="GF4" t="s">
+        <v>139</v>
+      </c>
       <c r="GY4">
         <v>90</v>
       </c>
@@ -3223,11 +3235,11 @@
       </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="63">COUNTIF(AI4:PR4,"HG")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="64">COUNTIF(CY4:GX4,"HG")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="65">COUNTIF(GY4:IT4,"HG")</f>
@@ -3248,11 +3260,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1661</v>
+        <v>1751</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>1051</v>
+        <v>1141</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3268,11 +3280,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3284,11 +3296,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3530,6 +3542,12 @@
       </c>
       <c r="GB5" t="s">
         <v>136</v>
+      </c>
+      <c r="GE5">
+        <v>90</v>
+      </c>
+      <c r="GF5" t="s">
+        <v>110</v>
       </c>
       <c r="HD5" t="s">
         <v>139</v>
@@ -3817,6 +3835,9 @@
       <c r="GB6" t="s">
         <v>139</v>
       </c>
+      <c r="GF6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3861,11 +3882,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3886,11 +3907,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2208</v>
+        <v>2298</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1363</v>
+        <v>1453</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3906,11 +3927,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3922,11 +3943,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -3978,11 +3999,11 @@
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="25"/>
@@ -3990,7 +4011,7 @@
       </c>
       <c r="AB7">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="27"/>
@@ -4156,6 +4177,15 @@
       </c>
       <c r="GB7" t="s">
         <v>110</v>
+      </c>
+      <c r="GE7">
+        <v>90</v>
+      </c>
+      <c r="GF7" t="s">
+        <v>110</v>
+      </c>
+      <c r="GH7">
+        <v>1</v>
       </c>
       <c r="GY7">
         <v>90</v>
@@ -4458,6 +4488,9 @@
       <c r="GB8" t="s">
         <v>139</v>
       </c>
+      <c r="GF8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4535,11 +4568,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4560,11 +4593,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2407</v>
+        <v>2497</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1651</v>
+        <v>1741</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4580,11 +4613,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4596,11 +4629,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4856,6 +4889,12 @@
         <v>90</v>
       </c>
       <c r="GB9" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE9">
+        <v>90</v>
+      </c>
+      <c r="GF9" t="s">
         <v>110</v>
       </c>
       <c r="HC9">
@@ -4927,11 +4966,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1601</v>
+        <v>1674</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>1001</v>
+        <v>1074</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4947,11 +4986,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -4963,11 +5002,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5199,6 +5238,12 @@
         <v>90</v>
       </c>
       <c r="GB10" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE10">
+        <v>73</v>
+      </c>
+      <c r="GF10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5273,11 +5318,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5293,7 +5338,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5301,7 +5346,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5309,7 +5354,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5317,7 +5362,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5525,6 +5570,12 @@
       </c>
       <c r="GB11" t="s">
         <v>139</v>
+      </c>
+      <c r="GE11">
+        <v>17</v>
+      </c>
+      <c r="GF11" t="s">
+        <v>136</v>
       </c>
       <c r="GY11">
         <v>90</v>
@@ -6077,6 +6128,9 @@
       <c r="GB13" t="s">
         <v>139</v>
       </c>
+      <c r="GF13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -6097,11 +6151,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6122,11 +6176,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>2031</v>
+        <v>2121</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>933</v>
+        <v>1023</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6142,11 +6196,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
@@ -6158,11 +6212,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
@@ -6206,11 +6260,11 @@
       </c>
       <c r="W14" s="3">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X14" s="4">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="23"/>
@@ -6222,7 +6276,7 @@
       </c>
       <c r="AA14">
         <f t="shared" si="25"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB14">
         <f t="shared" si="26"/>
@@ -6425,6 +6479,15 @@
       </c>
       <c r="GB14" t="s">
         <v>136</v>
+      </c>
+      <c r="GE14">
+        <v>90</v>
+      </c>
+      <c r="GF14" t="s">
+        <v>110</v>
+      </c>
+      <c r="GG14">
+        <v>1</v>
       </c>
       <c r="GY14">
         <v>90</v>
@@ -6519,11 +6582,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1487</v>
+        <v>1551</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>814</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6539,11 +6602,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6555,11 +6618,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
@@ -6828,6 +6891,12 @@
       </c>
       <c r="GB15" t="s">
         <v>136</v>
+      </c>
+      <c r="GE15">
+        <v>64</v>
+      </c>
+      <c r="GF15" t="s">
+        <v>110</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7545,11 +7614,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1503</v>
+        <v>1548</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>869</v>
+        <v>914</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7565,11 +7634,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7581,11 +7650,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7844,6 +7913,12 @@
         <v>74</v>
       </c>
       <c r="GB18" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE18">
+        <v>45</v>
+      </c>
+      <c r="GF18" t="s">
         <v>110</v>
       </c>
       <c r="GY18">
@@ -7921,11 +7996,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1183</v>
+        <v>1209</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -7941,7 +8016,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
@@ -7949,7 +8024,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="9"/>
@@ -7957,7 +8032,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
@@ -7965,7 +8040,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="13"/>
@@ -8179,6 +8254,12 @@
       </c>
       <c r="GB19" t="s">
         <v>139</v>
+      </c>
+      <c r="GE19">
+        <v>26</v>
+      </c>
+      <c r="GF19" t="s">
+        <v>136</v>
       </c>
       <c r="GY19">
         <v>72</v>
@@ -8598,6 +8679,9 @@
       <c r="GB20" t="s">
         <v>136</v>
       </c>
+      <c r="GF20" t="s">
+        <v>139</v>
+      </c>
       <c r="GY20">
         <v>31</v>
       </c>
@@ -8654,11 +8738,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -9239,6 +9323,9 @@
       <c r="GB22" t="s">
         <v>110</v>
       </c>
+      <c r="GF22" t="s">
+        <v>139</v>
+      </c>
       <c r="GY22">
         <v>90</v>
       </c>
@@ -9295,11 +9382,11 @@
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="35"/>
@@ -9540,11 +9627,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2267</v>
+        <v>2357</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1575</v>
+        <v>1665</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9560,11 +9647,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9576,11 +9663,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9818,6 +9905,12 @@
         <v>90</v>
       </c>
       <c r="GB24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE24">
+        <v>90</v>
+      </c>
+      <c r="GF24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10184,11 +10277,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>1100</v>
+        <v>1126</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
@@ -10204,7 +10297,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
@@ -10212,7 +10305,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="9"/>
@@ -10220,7 +10313,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="11"/>
@@ -10228,7 +10321,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="13"/>
@@ -10268,11 +10361,11 @@
       </c>
       <c r="W26" s="3">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X26" s="4">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="23"/>
@@ -10284,7 +10377,7 @@
       </c>
       <c r="AA26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26">
         <f t="shared" si="26"/>
@@ -10433,6 +10526,15 @@
       </c>
       <c r="GB26" t="s">
         <v>139</v>
+      </c>
+      <c r="GE26">
+        <v>26</v>
+      </c>
+      <c r="GF26" t="s">
+        <v>136</v>
+      </c>
+      <c r="GG26">
+        <v>1</v>
       </c>
       <c r="GY26">
         <v>72</v>
@@ -10574,7 +10676,7 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
@@ -10590,7 +10692,7 @@
       </c>
       <c r="N27" s="3">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <f t="shared" si="14"/>
@@ -10788,6 +10890,9 @@
       </c>
       <c r="GB27" t="s">
         <v>110</v>
+      </c>
+      <c r="GF27" t="s">
+        <v>138</v>
       </c>
       <c r="HD27" t="s">
         <v>139</v>
@@ -11165,11 +11270,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>1032</v>
+        <v>1096</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>792</v>
+        <v>856</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11185,11 +11290,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11201,11 +11306,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11392,6 +11497,12 @@
         <v>82</v>
       </c>
       <c r="GB29" t="s">
+        <v>110</v>
+      </c>
+      <c r="GE29">
+        <v>64</v>
+      </c>
+      <c r="GF29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -11644,6 +11755,9 @@
       <c r="GB30" t="s">
         <v>139</v>
       </c>
+      <c r="GF30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
@@ -11658,11 +11772,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -11683,11 +11797,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11703,11 +11817,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11719,11 +11833,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11767,27 +11881,27 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ref="Z31" si="128">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC31">
         <f t="shared" ref="AC31" si="131">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
@@ -11872,6 +11986,18 @@
       </c>
       <c r="GB31" t="s">
         <v>110</v>
+      </c>
+      <c r="GE31">
+        <v>90</v>
+      </c>
+      <c r="GF31" t="s">
+        <v>110</v>
+      </c>
+      <c r="GG31">
+        <v>4</v>
+      </c>
+      <c r="GH31">
+        <v>1</v>
       </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
@@ -11900,11 +12026,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>410</v>
+        <v>455</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -11920,7 +12046,7 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
@@ -11928,7 +12054,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -11936,7 +12062,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -11944,7 +12070,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -12083,6 +12209,12 @@
       </c>
       <c r="GB32" t="s">
         <v>110</v>
+      </c>
+      <c r="GE32">
+        <v>45</v>
+      </c>
+      <c r="GF32" t="s">
+        <v>136</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A09E1E-FA33-C34D-971F-A901BAFB4D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA34C764-95FC-DE4A-8009-14740663A4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>2085</v>
+        <v>2175</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1800</v>
+        <v>1890</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2581,6 +2581,12 @@
         <v>90</v>
       </c>
       <c r="GF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI2">
+        <v>90</v>
+      </c>
+      <c r="GJ2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2628,7 +2634,7 @@
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>810</v>
+        <v>900</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C29" si="2">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
@@ -2640,7 +2646,7 @@
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E29" si="4">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F30" si="5">SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3)</f>
@@ -2648,11 +2654,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G29" si="6">SUM(H3:I3)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H29" si="7">COUNTIF(AI3:PR3,"T")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I29" si="8">COUNTIF(AI3:PR3,"R")</f>
@@ -2696,11 +2702,11 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S29" si="18">SUM(T3:U3)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" s="3">
         <f t="shared" ref="T3:T29" si="19">COUNTIF(IU3:PR3,"T")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U3" s="3">
         <f t="shared" ref="U3:U29" si="20">COUNTIF(IU3:PR3,"R")</f>
@@ -2836,6 +2842,9 @@
       <c r="GF3" t="s">
         <v>139</v>
       </c>
+      <c r="GJ3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2894,6 +2903,12 @@
         <v>90</v>
       </c>
       <c r="KZ3" t="s">
+        <v>110</v>
+      </c>
+      <c r="LG3">
+        <v>90</v>
+      </c>
+      <c r="LH3" t="s">
         <v>110</v>
       </c>
       <c r="ME3">
@@ -2904,11 +2919,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2961,7 +2976,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2977,7 +2992,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3160,6 +3175,9 @@
       </c>
       <c r="GF4" t="s">
         <v>139</v>
+      </c>
+      <c r="GJ4" t="s">
+        <v>138</v>
       </c>
       <c r="GY4">
         <v>90</v>
@@ -3260,11 +3278,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1751</v>
+        <v>1841</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>1141</v>
+        <v>1231</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3280,11 +3298,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3296,11 +3314,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3547,6 +3565,12 @@
         <v>90</v>
       </c>
       <c r="GF5" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI5">
+        <v>90</v>
+      </c>
+      <c r="GJ5" t="s">
         <v>110</v>
       </c>
       <c r="HD5" t="s">
@@ -3838,6 +3862,9 @@
       <c r="GF6" t="s">
         <v>139</v>
       </c>
+      <c r="GJ6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3882,11 +3909,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3907,11 +3934,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2298</v>
+        <v>2388</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1453</v>
+        <v>1543</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3927,11 +3954,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3943,11 +3970,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4186,6 +4213,12 @@
       </c>
       <c r="GH7">
         <v>1</v>
+      </c>
+      <c r="GI7">
+        <v>90</v>
+      </c>
+      <c r="GJ7" t="s">
+        <v>110</v>
       </c>
       <c r="GY7">
         <v>90</v>
@@ -4491,6 +4524,9 @@
       <c r="GF8" t="s">
         <v>139</v>
       </c>
+      <c r="GJ8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4568,11 +4604,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4593,11 +4629,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2497</v>
+        <v>2587</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1741</v>
+        <v>1831</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4613,11 +4649,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4629,11 +4665,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4895,6 +4931,12 @@
         <v>90</v>
       </c>
       <c r="GF9" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI9">
+        <v>90</v>
+      </c>
+      <c r="GJ9" t="s">
         <v>110</v>
       </c>
       <c r="HC9">
@@ -4966,11 +5008,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1674</v>
+        <v>1764</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>1074</v>
+        <v>1164</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -4986,11 +5028,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -5002,11 +5044,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5244,6 +5286,12 @@
         <v>73</v>
       </c>
       <c r="GF10" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI10">
+        <v>90</v>
+      </c>
+      <c r="GJ10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5318,11 +5366,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5338,7 +5386,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5346,7 +5394,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5354,7 +5402,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5362,7 +5410,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5575,6 +5623,12 @@
         <v>17</v>
       </c>
       <c r="GF11" t="s">
+        <v>136</v>
+      </c>
+      <c r="GI11">
+        <v>1</v>
+      </c>
+      <c r="GJ11" t="s">
         <v>136</v>
       </c>
       <c r="GY11">
@@ -6131,6 +6185,9 @@
       <c r="GF13" t="s">
         <v>139</v>
       </c>
+      <c r="GJ13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -6151,11 +6208,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6176,11 +6233,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>2121</v>
+        <v>2210</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>1023</v>
+        <v>1112</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6196,11 +6253,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
@@ -6212,11 +6269,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
@@ -6260,27 +6317,27 @@
       </c>
       <c r="W14" s="3">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X14" s="4">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z14" s="4">
         <f t="shared" si="24"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB14">
         <f t="shared" si="26"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC14">
         <f t="shared" si="27"/>
@@ -6487,6 +6544,18 @@
         <v>110</v>
       </c>
       <c r="GG14">
+        <v>1</v>
+      </c>
+      <c r="GI14">
+        <v>89</v>
+      </c>
+      <c r="GJ14" t="s">
+        <v>110</v>
+      </c>
+      <c r="GK14">
+        <v>1</v>
+      </c>
+      <c r="GL14">
         <v>1</v>
       </c>
       <c r="GY14">
@@ -6582,11 +6651,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1551</v>
+        <v>1573</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6602,7 +6671,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
@@ -6610,7 +6679,7 @@
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="3">
         <f t="shared" si="9"/>
@@ -6618,7 +6687,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
@@ -6626,7 +6695,7 @@
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N15" s="3">
         <f t="shared" si="13"/>
@@ -6897,6 +6966,12 @@
       </c>
       <c r="GF15" t="s">
         <v>110</v>
+      </c>
+      <c r="GI15">
+        <v>22</v>
+      </c>
+      <c r="GJ15" t="s">
+        <v>136</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7614,11 +7689,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1548</v>
+        <v>1616</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>914</v>
+        <v>982</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7634,11 +7709,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7650,11 +7725,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7919,6 +7994,12 @@
         <v>45</v>
       </c>
       <c r="GF18" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI18">
+        <v>68</v>
+      </c>
+      <c r="GJ18" t="s">
         <v>110</v>
       </c>
       <c r="GY18">
@@ -7996,11 +8077,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1209</v>
+        <v>1277</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>423</v>
+        <v>491</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -8016,11 +8097,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
@@ -8032,11 +8113,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
@@ -8260,6 +8341,12 @@
       </c>
       <c r="GF19" t="s">
         <v>136</v>
+      </c>
+      <c r="GI19">
+        <v>68</v>
+      </c>
+      <c r="GJ19" t="s">
+        <v>110</v>
       </c>
       <c r="GY19">
         <v>72</v>
@@ -8682,6 +8769,9 @@
       <c r="GF20" t="s">
         <v>139</v>
       </c>
+      <c r="GJ20" t="s">
+        <v>139</v>
+      </c>
       <c r="GY20">
         <v>31</v>
       </c>
@@ -8738,11 +8828,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -9326,6 +9416,9 @@
       <c r="GF22" t="s">
         <v>139</v>
       </c>
+      <c r="GJ22" t="s">
+        <v>139</v>
+      </c>
       <c r="GY22">
         <v>90</v>
       </c>
@@ -9382,11 +9475,11 @@
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="35"/>
@@ -9627,11 +9720,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2357</v>
+        <v>2447</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1665</v>
+        <v>1755</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9647,11 +9740,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9663,11 +9756,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -9911,6 +10004,12 @@
         <v>90</v>
       </c>
       <c r="GF24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI24">
+        <v>90</v>
+      </c>
+      <c r="GJ24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10277,11 +10376,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
@@ -10297,7 +10396,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
@@ -10305,7 +10404,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="9"/>
@@ -10313,7 +10412,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="11"/>
@@ -10321,7 +10420,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="13"/>
@@ -10535,6 +10634,12 @@
       </c>
       <c r="GG26">
         <v>1</v>
+      </c>
+      <c r="GI26">
+        <v>9</v>
+      </c>
+      <c r="GJ26" t="s">
+        <v>136</v>
       </c>
       <c r="GY26">
         <v>72</v>
@@ -10894,6 +10999,9 @@
       <c r="GF27" t="s">
         <v>138</v>
       </c>
+      <c r="GJ27" t="s">
+        <v>139</v>
+      </c>
       <c r="HD27" t="s">
         <v>139</v>
       </c>
@@ -10929,11 +11037,11 @@
       </c>
       <c r="PS27" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="34"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="35"/>
@@ -11270,11 +11378,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>1096</v>
+        <v>1186</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>856</v>
+        <v>946</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11290,11 +11398,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11306,11 +11414,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11503,6 +11611,12 @@
         <v>64</v>
       </c>
       <c r="GF29" t="s">
+        <v>110</v>
+      </c>
+      <c r="GI29">
+        <v>90</v>
+      </c>
+      <c r="GJ29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -11758,6 +11872,9 @@
       <c r="GF30" t="s">
         <v>139</v>
       </c>
+      <c r="GJ30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
@@ -11772,11 +11889,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -11797,11 +11914,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>690</v>
+        <v>771</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>690</v>
+        <v>771</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -11817,11 +11934,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -11833,11 +11950,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -11881,27 +11998,27 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ref="Z31" si="128">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC31">
         <f t="shared" ref="AC31" si="131">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
@@ -11997,6 +12114,18 @@
         <v>4</v>
       </c>
       <c r="GH31">
+        <v>1</v>
+      </c>
+      <c r="GI31">
+        <v>81</v>
+      </c>
+      <c r="GJ31" t="s">
+        <v>110</v>
+      </c>
+      <c r="GK31">
+        <v>1</v>
+      </c>
+      <c r="GL31">
         <v>1</v>
       </c>
       <c r="PS31" s="3">
@@ -12026,11 +12155,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -12046,7 +12175,7 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
@@ -12054,7 +12183,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -12062,7 +12191,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -12070,7 +12199,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -12110,11 +12239,11 @@
       </c>
       <c r="W32" s="3">
         <f t="shared" ref="W32" si="163">SUM(AK32,AO32,AS32,AW32,BA32,BE32,BI32,BM32,BQ32,BU32,BY32,CC32,CG32,CK32,CO32,CS32,CW32,DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MG32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X32" s="4">
         <f t="shared" ref="X32" si="164">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32,HA32,HE32,HI32,HM32,HQ32,HU32,HY32,IC32,IG32,IK32,IO32,IS32,IW32,JA32,JE32,JI32,JM32,JQ32,JU32,JY32,KC32,KG32,KK32,KO32,KS32,KW32,LA32,LE32,LI32,LM32,LQ32,LU32,LY32,MC32,MG32,MK32,MO32,MS32,MW32,NA32,NE32,NI32,NM32,NQ32,NU32,NY32,OC32,OG32,OK32,OO32,OS32,OW32,PA32,PE32,PI32,PM32,PQ32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y32" s="4">
         <f t="shared" ref="Y32" si="165">SUM(AL32,AP32,AT32,AX32,BB32,BF32,BJ32,BN32,BR32,BV32,BZ32,CD32,CH32,CL32,CP32,CT32,CX32,DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32,HB32,HF32,HJ32,HN32,HR32,HV32,HZ32,ID32,IH32,IL32,IP32,IT32,IX32,JB32,JF32,JJ32,JN32,JR32,JV32,JZ32,KD32,KH32,KL32,KP32,KT32,KX32,LB32,LF32,LJ32,LN32,LR32,LV32,LZ32,MD32,MH32,ML32,MP32,MT32,MX32,NB32,NF32,NJ32,NN32,NR32,NV32,NZ32,OD32,OH32,OL32,OP32,OT32,OX32,PB32,PF32,PJ32,PN32,PR32)</f>
@@ -12126,7 +12255,7 @@
       </c>
       <c r="AA32">
         <f t="shared" ref="AA32" si="167">SUM(DA32,DE32,DI32,DM32,DQ32,DU32,DY32,EC32,EG32,EK32,EO32,ES32,EW32,FA32,FE32,FI32,FM32,FQ32,FU32,FY32,GC32,GG32,GK32,GO32,GS32,GW32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB32">
         <f t="shared" ref="AB32" si="168">SUM(DB32,DF32,DJ32,DN32,DR32,DV32,DZ32,ED32,EH32,EL32,EP32,ET32,EX32,FB32,FF32,FJ32,FN32,FR32,FV32,FZ32,GD32,GH32,GL32,GP32,GT32,GX32)</f>
@@ -12215,6 +12344,15 @@
       </c>
       <c r="GF32" t="s">
         <v>136</v>
+      </c>
+      <c r="GI32">
+        <v>22</v>
+      </c>
+      <c r="GJ32" t="s">
+        <v>136</v>
+      </c>
+      <c r="GK32">
+        <v>2</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA34C764-95FC-DE4A-8009-14740663A4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5B07A9-6F6C-8A4A-AF49-68B8FE5E1D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="Y2" s="4">
         <f>SUM(AL2,AP2,AT2,AX2,BB2,BF2,BJ2,BN2,BR2,BV2,BZ2,CD2,CH2,CL2,CP2,CT2,CX2,DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,MH2,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="4">
         <f>SUM(DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2,HB2,HF2,HJ2,HN2,HR2,HV2,HZ2,ID2,IH2,IL2,IP2,IT2,IX2,JB2,JF2,JJ2,JN2,JR2,JV2,JZ2,KD2,KH2,KL2,KP2,KT2,KX2,LB2,LF2,LJ2,LN2,LR2,LV2,LZ2,MD2,MH2,ML2,MP2,MT2,MX2,NB2,NF2,NJ2,NN2,NR2,NV2,NZ2,OD2,OH2,OL2,OP2,OT2,OX2,PB2,PF2,PJ2,PN2,PR2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2">
         <f>SUM(DA2,DE2,DI2,DM2,DQ2,DU2,DY2,EC2,EG2,EK2,EO2,ES2,EW2,FA2,FE2,FI2,FM2,FQ2,FU2,FY2,GC2,GG2,GK2,GO2,GS2,GW2)</f>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="AB2">
         <f>SUM(DB2,DF2,DJ2,DN2,DR2,DV2,DZ2,ED2,EH2,EL2,EP2,ET2,EX2,FB2,FF2,FJ2,FN2,FR2,FV2,FZ2,GD2,GH2,GL2,GP2,GT2,GX2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2">
         <f>SUM(HA2,HE2,HI2,HM2,HQ2,HU2,HY2,IC2,IG2,IK2,IO2,IS2)</f>
@@ -2588,6 +2588,9 @@
       </c>
       <c r="GJ2" t="s">
         <v>110</v>
+      </c>
+      <c r="GL2">
+        <v>1</v>
       </c>
       <c r="HD2" t="s">
         <v>138</v>
@@ -6743,11 +6746,11 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="4">
         <f t="shared" si="24"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA15">
         <f t="shared" si="25"/>
@@ -6755,7 +6758,7 @@
       </c>
       <c r="AB15">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC15">
         <f t="shared" si="27"/>
@@ -6972,6 +6975,9 @@
       </c>
       <c r="GJ15" t="s">
         <v>136</v>
+      </c>
+      <c r="GL15">
+        <v>1</v>
       </c>
       <c r="GY15">
         <v>59</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5B07A9-6F6C-8A4A-AF49-68B8FE5E1D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86A7298-3773-3848-AF84-F1576A398496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>2175</v>
+        <v>2265</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1890</v>
+        <v>1980</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2591,6 +2591,12 @@
       </c>
       <c r="GL2">
         <v>1</v>
+      </c>
+      <c r="GM2">
+        <v>90</v>
+      </c>
+      <c r="GN2" t="s">
+        <v>110</v>
       </c>
       <c r="HD2" t="s">
         <v>138</v>
@@ -2848,6 +2854,9 @@
       <c r="GJ3" t="s">
         <v>139</v>
       </c>
+      <c r="GN3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2922,11 +2931,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2979,7 +2988,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -2995,7 +3004,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3180,6 +3189,9 @@
         <v>139</v>
       </c>
       <c r="GJ4" t="s">
+        <v>138</v>
+      </c>
+      <c r="GN4" t="s">
         <v>138</v>
       </c>
       <c r="GY4">
@@ -3281,11 +3293,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="37"/>
-        <v>1841</v>
+        <v>1919</v>
       </c>
       <c r="C5">
         <f t="shared" si="2"/>
-        <v>1231</v>
+        <v>1309</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -3301,11 +3313,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="8"/>
@@ -3317,11 +3329,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="12"/>
@@ -3574,6 +3586,12 @@
         <v>90</v>
       </c>
       <c r="GJ5" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM5">
+        <v>78</v>
+      </c>
+      <c r="GN5" t="s">
         <v>110</v>
       </c>
       <c r="HD5" t="s">
@@ -3868,6 +3886,9 @@
       <c r="GJ6" t="s">
         <v>139</v>
       </c>
+      <c r="GN6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3912,11 +3933,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3937,11 +3958,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2388</v>
+        <v>2478</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1543</v>
+        <v>1633</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3957,11 +3978,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3973,11 +3994,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4221,6 +4242,12 @@
         <v>90</v>
       </c>
       <c r="GJ7" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM7">
+        <v>90</v>
+      </c>
+      <c r="GN7" t="s">
         <v>110</v>
       </c>
       <c r="GY7">
@@ -4530,6 +4557,9 @@
       <c r="GJ8" t="s">
         <v>139</v>
       </c>
+      <c r="GN8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4607,11 +4637,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4632,11 +4662,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2587</v>
+        <v>2632</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1831</v>
+        <v>1876</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4652,7 +4682,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
@@ -4660,7 +4690,7 @@
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="9"/>
@@ -4668,7 +4698,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
@@ -4676,7 +4706,7 @@
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="13"/>
@@ -4716,11 +4746,11 @@
       </c>
       <c r="W9" s="3">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="4">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="4">
         <f t="shared" si="23"/>
@@ -4732,7 +4762,7 @@
       </c>
       <c r="AA9">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9">
         <f t="shared" si="26"/>
@@ -4941,6 +4971,15 @@
       </c>
       <c r="GJ9" t="s">
         <v>110</v>
+      </c>
+      <c r="GM9">
+        <v>45</v>
+      </c>
+      <c r="GN9" t="s">
+        <v>136</v>
+      </c>
+      <c r="GO9">
+        <v>1</v>
       </c>
       <c r="HC9">
         <v>45</v>
@@ -5011,11 +5050,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1764</v>
+        <v>1838</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>1164</v>
+        <v>1238</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -5031,11 +5070,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -5047,11 +5086,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5295,6 +5334,12 @@
         <v>90</v>
       </c>
       <c r="GJ10" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM10">
+        <v>74</v>
+      </c>
+      <c r="GN10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5369,11 +5414,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1247</v>
+        <v>1263</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5389,7 +5434,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5397,7 +5442,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5405,7 +5450,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5413,7 +5458,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5632,6 +5677,12 @@
         <v>1</v>
       </c>
       <c r="GJ11" t="s">
+        <v>136</v>
+      </c>
+      <c r="GM11">
+        <v>16</v>
+      </c>
+      <c r="GN11" t="s">
         <v>136</v>
       </c>
       <c r="GY11">
@@ -6191,6 +6242,9 @@
       <c r="GJ13" t="s">
         <v>139</v>
       </c>
+      <c r="GN13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -6211,11 +6265,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6236,11 +6290,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>2210</v>
+        <v>2300</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>1112</v>
+        <v>1202</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6256,11 +6310,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
@@ -6272,11 +6326,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
@@ -6560,6 +6614,12 @@
       </c>
       <c r="GL14">
         <v>1</v>
+      </c>
+      <c r="GM14">
+        <v>90</v>
+      </c>
+      <c r="GN14" t="s">
+        <v>110</v>
       </c>
       <c r="GY14">
         <v>90</v>
@@ -6654,11 +6714,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1573</v>
+        <v>1663</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>836</v>
+        <v>926</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6674,11 +6734,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6690,11 +6750,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
@@ -6738,11 +6798,11 @@
       </c>
       <c r="W15" s="3">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15" s="4">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="23"/>
@@ -6754,7 +6814,7 @@
       </c>
       <c r="AA15">
         <f t="shared" si="25"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB15">
         <f t="shared" si="26"/>
@@ -6977,6 +7037,15 @@
         <v>136</v>
       </c>
       <c r="GL15">
+        <v>1</v>
+      </c>
+      <c r="GM15">
+        <v>90</v>
+      </c>
+      <c r="GN15" t="s">
+        <v>110</v>
+      </c>
+      <c r="GO15">
         <v>1</v>
       </c>
       <c r="GY15">
@@ -7695,11 +7764,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1616</v>
+        <v>1706</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>982</v>
+        <v>1072</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7715,11 +7784,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7731,11 +7800,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -8006,6 +8075,12 @@
         <v>68</v>
       </c>
       <c r="GJ18" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM18">
+        <v>90</v>
+      </c>
+      <c r="GN18" t="s">
         <v>110</v>
       </c>
       <c r="GY18">
@@ -8083,11 +8158,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1277</v>
+        <v>1322</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -8103,11 +8178,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
@@ -8119,11 +8194,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
@@ -8352,6 +8427,12 @@
         <v>68</v>
       </c>
       <c r="GJ19" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM19">
+        <v>45</v>
+      </c>
+      <c r="GN19" t="s">
         <v>110</v>
       </c>
       <c r="GY19">
@@ -8778,6 +8859,9 @@
       <c r="GJ20" t="s">
         <v>139</v>
       </c>
+      <c r="GN20" t="s">
+        <v>139</v>
+      </c>
       <c r="GY20">
         <v>31</v>
       </c>
@@ -8834,11 +8918,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -9425,6 +9509,9 @@
       <c r="GJ22" t="s">
         <v>139</v>
       </c>
+      <c r="GN22" t="s">
+        <v>139</v>
+      </c>
       <c r="GY22">
         <v>90</v>
       </c>
@@ -9481,11 +9568,11 @@
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="35"/>
@@ -9726,11 +9813,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2447</v>
+        <v>2492</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1755</v>
+        <v>1800</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9746,11 +9833,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9762,11 +9849,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -10016,6 +10103,12 @@
         <v>90</v>
       </c>
       <c r="GJ24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM24">
+        <v>45</v>
+      </c>
+      <c r="GN24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10382,11 +10475,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
@@ -10402,7 +10495,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
@@ -10410,7 +10503,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="9"/>
@@ -10418,7 +10511,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="11"/>
@@ -10426,7 +10519,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="13"/>
@@ -10645,6 +10738,12 @@
         <v>9</v>
       </c>
       <c r="GJ26" t="s">
+        <v>136</v>
+      </c>
+      <c r="GM26">
+        <v>12</v>
+      </c>
+      <c r="GN26" t="s">
         <v>136</v>
       </c>
       <c r="GY26">
@@ -10755,11 +10854,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>1927</v>
+        <v>2017</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1432</v>
+        <v>1522</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10775,11 +10874,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10791,11 +10890,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -11007,6 +11106,12 @@
       </c>
       <c r="GJ27" t="s">
         <v>139</v>
+      </c>
+      <c r="GM27">
+        <v>90</v>
+      </c>
+      <c r="GN27" t="s">
+        <v>110</v>
       </c>
       <c r="HD27" t="s">
         <v>139</v>
@@ -11384,11 +11489,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>1186</v>
+        <v>1276</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>946</v>
+        <v>1036</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11404,11 +11509,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11420,11 +11525,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11623,6 +11728,12 @@
         <v>90</v>
       </c>
       <c r="GJ29" t="s">
+        <v>110</v>
+      </c>
+      <c r="GM29">
+        <v>90</v>
+      </c>
+      <c r="GN29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -11881,6 +11992,9 @@
       <c r="GJ30" t="s">
         <v>139</v>
       </c>
+      <c r="GN30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
@@ -11895,11 +12009,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -12134,13 +12248,16 @@
       <c r="GL31">
         <v>1</v>
       </c>
+      <c r="GN31" t="s">
+        <v>139</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="138">COUNTIF(CY31:GX31,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="139">COUNTIF(GY31:IT31,"HG")</f>
@@ -12161,11 +12278,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -12181,7 +12298,7 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
@@ -12189,7 +12306,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -12197,7 +12314,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -12205,7 +12322,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -12359,6 +12476,12 @@
       </c>
       <c r="GK32">
         <v>2</v>
+      </c>
+      <c r="GM32">
+        <v>45</v>
+      </c>
+      <c r="GN32" t="s">
+        <v>136</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86A7298-3773-3848-AF84-F1576A398496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B55B9B-0359-9348-A914-15A735524F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5">
         <f t="shared" si="25"/>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AB5">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5">
         <f t="shared" si="27"/>
@@ -3593,6 +3593,9 @@
       </c>
       <c r="GN5" t="s">
         <v>110</v>
+      </c>
+      <c r="GP5">
+        <v>1</v>
       </c>
       <c r="HD5" t="s">
         <v>139</v>
@@ -6806,11 +6809,11 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z15" s="4">
         <f t="shared" si="24"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA15">
         <f t="shared" si="25"/>
@@ -6818,7 +6821,7 @@
       </c>
       <c r="AB15">
         <f t="shared" si="26"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC15">
         <f t="shared" si="27"/>
@@ -7046,6 +7049,9 @@
         <v>110</v>
       </c>
       <c r="GO15">
+        <v>1</v>
+      </c>
+      <c r="GP15">
         <v>1</v>
       </c>
       <c r="GY15">

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B55B9B-0359-9348-A914-15A735524F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCF8977-04DE-9A4C-941E-02C630B8BBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>2265</v>
+        <v>2355</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>1980</v>
+        <v>2070</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2596,6 +2596,12 @@
         <v>90</v>
       </c>
       <c r="GN2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ2">
+        <v>90</v>
+      </c>
+      <c r="GR2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2857,6 +2863,9 @@
       <c r="GN3" t="s">
         <v>139</v>
       </c>
+      <c r="GR3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2931,11 +2940,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2988,7 +2997,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -3004,7 +3013,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3192,6 +3201,9 @@
         <v>138</v>
       </c>
       <c r="GN4" t="s">
+        <v>138</v>
+      </c>
+      <c r="GR4" t="s">
         <v>138</v>
       </c>
       <c r="GY4">
@@ -3597,6 +3609,9 @@
       <c r="GP5">
         <v>1</v>
       </c>
+      <c r="GR5" t="s">
+        <v>139</v>
+      </c>
       <c r="HD5" t="s">
         <v>139</v>
       </c>
@@ -3626,11 +3641,11 @@
       </c>
       <c r="PS5" s="3">
         <f t="shared" si="33"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="PT5" s="3">
         <f t="shared" si="34"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU5" s="3">
         <f t="shared" si="35"/>
@@ -3892,6 +3907,9 @@
       <c r="GN6" t="s">
         <v>139</v>
       </c>
+      <c r="GR6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3936,11 +3954,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3961,11 +3979,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2478</v>
+        <v>2568</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1633</v>
+        <v>1723</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3981,11 +3999,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -3997,11 +4015,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4251,6 +4269,12 @@
         <v>90</v>
       </c>
       <c r="GN7" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ7">
+        <v>90</v>
+      </c>
+      <c r="GR7" t="s">
         <v>110</v>
       </c>
       <c r="GY7">
@@ -4563,6 +4587,9 @@
       <c r="GN8" t="s">
         <v>139</v>
       </c>
+      <c r="GR8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4640,11 +4667,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4665,11 +4692,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2632</v>
+        <v>2722</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1876</v>
+        <v>1966</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4685,11 +4712,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4701,11 +4728,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -4983,6 +5010,12 @@
       </c>
       <c r="GO9">
         <v>1</v>
+      </c>
+      <c r="GQ9">
+        <v>90</v>
+      </c>
+      <c r="GR9" t="s">
+        <v>110</v>
       </c>
       <c r="HC9">
         <v>45</v>
@@ -5053,11 +5086,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1838</v>
+        <v>1923</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>1238</v>
+        <v>1323</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -5073,11 +5106,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -5089,11 +5122,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5343,6 +5376,12 @@
         <v>74</v>
       </c>
       <c r="GN10" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ10">
+        <v>85</v>
+      </c>
+      <c r="GR10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5417,11 +5456,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5437,7 +5476,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5445,7 +5484,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5453,7 +5492,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5461,7 +5500,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5686,6 +5725,12 @@
         <v>16</v>
       </c>
       <c r="GN11" t="s">
+        <v>136</v>
+      </c>
+      <c r="GQ11">
+        <v>5</v>
+      </c>
+      <c r="GR11" t="s">
         <v>136</v>
       </c>
       <c r="GY11">
@@ -6248,6 +6293,9 @@
       <c r="GN13" t="s">
         <v>139</v>
       </c>
+      <c r="GR13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -6268,11 +6316,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6293,11 +6341,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>2300</v>
+        <v>2345</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>1202</v>
+        <v>1247</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6313,11 +6361,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
@@ -6329,11 +6377,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
@@ -6622,6 +6670,12 @@
         <v>90</v>
       </c>
       <c r="GN14" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ14">
+        <v>45</v>
+      </c>
+      <c r="GR14" t="s">
         <v>110</v>
       </c>
       <c r="GY14">
@@ -6717,11 +6771,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1663</v>
+        <v>1753</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>926</v>
+        <v>1016</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6737,11 +6791,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6753,11 +6807,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
@@ -7053,6 +7107,12 @@
       </c>
       <c r="GP15">
         <v>1</v>
+      </c>
+      <c r="GQ15">
+        <v>90</v>
+      </c>
+      <c r="GR15" t="s">
+        <v>110</v>
       </c>
       <c r="GY15">
         <v>59</v>
@@ -7770,11 +7830,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1706</v>
+        <v>1751</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>1072</v>
+        <v>1117</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7790,7 +7850,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
@@ -7798,7 +7858,7 @@
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="9"/>
@@ -7806,7 +7866,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
@@ -7814,7 +7874,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="13"/>
@@ -7854,11 +7914,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="21"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="23"/>
@@ -7870,7 +7930,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -8088,6 +8148,15 @@
       </c>
       <c r="GN18" t="s">
         <v>110</v>
+      </c>
+      <c r="GQ18">
+        <v>45</v>
+      </c>
+      <c r="GR18" t="s">
+        <v>136</v>
+      </c>
+      <c r="GS18">
+        <v>1</v>
       </c>
       <c r="GY18">
         <v>18</v>
@@ -8164,11 +8233,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -8184,7 +8253,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
@@ -8192,7 +8261,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="9"/>
@@ -8200,7 +8269,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
@@ -8208,7 +8277,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="13"/>
@@ -8248,11 +8317,11 @@
       </c>
       <c r="W19" s="3">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="4">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="23"/>
@@ -8264,7 +8333,7 @@
       </c>
       <c r="AA19">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
         <f t="shared" si="26"/>
@@ -8440,6 +8509,15 @@
       </c>
       <c r="GN19" t="s">
         <v>110</v>
+      </c>
+      <c r="GQ19">
+        <v>8</v>
+      </c>
+      <c r="GR19" t="s">
+        <v>136</v>
+      </c>
+      <c r="GS19">
+        <v>1</v>
       </c>
       <c r="GY19">
         <v>72</v>
@@ -8868,6 +8946,9 @@
       <c r="GN20" t="s">
         <v>139</v>
       </c>
+      <c r="GR20" t="s">
+        <v>139</v>
+      </c>
       <c r="GY20">
         <v>31</v>
       </c>
@@ -8924,11 +9005,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -9518,6 +9599,9 @@
       <c r="GN22" t="s">
         <v>139</v>
       </c>
+      <c r="GR22" t="s">
+        <v>139</v>
+      </c>
       <c r="GY22">
         <v>90</v>
       </c>
@@ -9574,11 +9658,11 @@
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="34"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="35"/>
@@ -9819,11 +9903,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2492</v>
+        <v>2582</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1800</v>
+        <v>1890</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9839,11 +9923,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9855,11 +9939,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -10115,6 +10199,12 @@
         <v>45</v>
       </c>
       <c r="GN24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ24">
+        <v>90</v>
+      </c>
+      <c r="GR24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10481,11 +10571,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="37"/>
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D26">
         <f t="shared" si="3"/>
@@ -10501,7 +10591,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="7"/>
@@ -10509,7 +10599,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="9"/>
@@ -10517,7 +10607,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="11"/>
@@ -10525,7 +10615,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="13"/>
@@ -10573,11 +10663,11 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26">
         <f t="shared" si="25"/>
@@ -10585,7 +10675,7 @@
       </c>
       <c r="AB26">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26">
         <f t="shared" si="27"/>
@@ -10751,6 +10841,15 @@
       </c>
       <c r="GN26" t="s">
         <v>136</v>
+      </c>
+      <c r="GQ26">
+        <v>1</v>
+      </c>
+      <c r="GR26" t="s">
+        <v>136</v>
+      </c>
+      <c r="GT26">
+        <v>1</v>
       </c>
       <c r="GY26">
         <v>72</v>
@@ -10860,11 +10959,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>2017</v>
+        <v>2107</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1522</v>
+        <v>1612</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10880,11 +10979,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10896,11 +10995,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -11117,6 +11216,12 @@
         <v>90</v>
       </c>
       <c r="GN27" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ27">
+        <v>90</v>
+      </c>
+      <c r="GR27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -11495,11 +11600,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>1276</v>
+        <v>1366</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>1036</v>
+        <v>1126</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11515,11 +11620,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11531,11 +11636,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11740,6 +11845,12 @@
         <v>90</v>
       </c>
       <c r="GN29" t="s">
+        <v>110</v>
+      </c>
+      <c r="GQ29">
+        <v>90</v>
+      </c>
+      <c r="GR29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -12001,6 +12112,9 @@
       <c r="GN30" t="s">
         <v>139</v>
       </c>
+      <c r="GR30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
@@ -12015,11 +12129,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -12040,11 +12154,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>771</v>
+        <v>860</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>771</v>
+        <v>860</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -12060,11 +12174,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -12076,11 +12190,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -12124,27 +12238,27 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ref="Z31" si="128">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC31">
         <f t="shared" ref="AC31" si="131">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
@@ -12256,6 +12370,18 @@
       </c>
       <c r="GN31" t="s">
         <v>139</v>
+      </c>
+      <c r="GQ31">
+        <v>89</v>
+      </c>
+      <c r="GR31" t="s">
+        <v>110</v>
+      </c>
+      <c r="GS31">
+        <v>2</v>
+      </c>
+      <c r="GT31">
+        <v>1</v>
       </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="137">COUNTIF(AI31:PR31,"HG")</f>
@@ -12284,11 +12410,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>522</v>
+        <v>604</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -12304,11 +12430,11 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
@@ -12320,11 +12446,11 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
@@ -12488,6 +12614,12 @@
       </c>
       <c r="GN32" t="s">
         <v>136</v>
+      </c>
+      <c r="GQ32">
+        <v>82</v>
+      </c>
+      <c r="GR32" t="s">
+        <v>110</v>
       </c>
       <c r="KQ32">
         <v>90</v>

--- a/data/Temps de jeu.xlsx
+++ b/data/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCF8977-04DE-9A4C-941E-02C630B8BBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9FE6AE-AEDF-E94E-BAE5-4829A1FCF8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2294,11 +2294,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>2355</v>
+        <v>2445</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>2070</v>
+        <v>2160</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2602,6 +2602,12 @@
         <v>90</v>
       </c>
       <c r="GR2" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU2">
+        <v>90</v>
+      </c>
+      <c r="GV2" t="s">
         <v>110</v>
       </c>
       <c r="HD2" t="s">
@@ -2866,6 +2872,9 @@
       <c r="GR3" t="s">
         <v>139</v>
       </c>
+      <c r="GV3" t="s">
+        <v>139</v>
+      </c>
       <c r="HD3" t="s">
         <v>139</v>
       </c>
@@ -2940,11 +2949,11 @@
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS29" si="33">COUNTIF(AI3:PR3,"HG")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT29" si="34">COUNTIF(CY3:GX3,"HG")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU29" si="35">COUNTIF(GY3:IT3,"HG")</f>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="J4" s="3">
         <f t="shared" ref="J4" si="41">COUNTIF(AI4:PR4,"NR")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4" si="42">SUM(L4:M4)</f>
@@ -3013,7 +3022,7 @@
       </c>
       <c r="N4" s="3">
         <f t="shared" ref="N4" si="45">COUNTIF(CY4:GX4,"NR")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4" si="46">SUM(P4:Q4)</f>
@@ -3204,6 +3213,9 @@
         <v>138</v>
       </c>
       <c r="GR4" t="s">
+        <v>138</v>
+      </c>
+      <c r="GV4" t="s">
         <v>138</v>
       </c>
       <c r="GY4">
@@ -3612,6 +3624,9 @@
       <c r="GR5" t="s">
         <v>139</v>
       </c>
+      <c r="GV5" t="s">
+        <v>139</v>
+      </c>
       <c r="HD5" t="s">
         <v>139</v>
       </c>
@@ -3641,11 +3656,11 @@
       </c>
       <c r="PS5" s="3">
         <f t="shared" si="33"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="PT5" s="3">
         <f t="shared" si="34"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PU5" s="3">
         <f t="shared" si="35"/>
@@ -3910,6 +3925,9 @@
       <c r="GR6" t="s">
         <v>139</v>
       </c>
+      <c r="GV6" t="s">
+        <v>139</v>
+      </c>
       <c r="HD6" t="s">
         <v>139</v>
       </c>
@@ -3954,11 +3972,11 @@
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="33"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="PT6" s="3">
         <f t="shared" si="34"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="PU6" s="3">
         <f t="shared" si="35"/>
@@ -3979,11 +3997,11 @@
       </c>
       <c r="B7">
         <f t="shared" si="37"/>
-        <v>2568</v>
+        <v>2613</v>
       </c>
       <c r="C7">
         <f t="shared" si="2"/>
-        <v>1723</v>
+        <v>1768</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -3999,11 +4017,11 @@
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="8"/>
@@ -4015,11 +4033,11 @@
       </c>
       <c r="K7">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="3">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="3">
         <f t="shared" si="12"/>
@@ -4275,6 +4293,12 @@
         <v>90</v>
       </c>
       <c r="GR7" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU7">
+        <v>45</v>
+      </c>
+      <c r="GV7" t="s">
         <v>110</v>
       </c>
       <c r="GY7">
@@ -4590,6 +4614,9 @@
       <c r="GR8" t="s">
         <v>139</v>
       </c>
+      <c r="GV8" t="s">
+        <v>139</v>
+      </c>
       <c r="GY8">
         <v>11</v>
       </c>
@@ -4667,11 +4694,11 @@
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="33"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="34"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="35"/>
@@ -4692,11 +4719,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="37"/>
-        <v>2722</v>
+        <v>2812</v>
       </c>
       <c r="C9">
         <f t="shared" si="2"/>
-        <v>1966</v>
+        <v>2056</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -4712,11 +4739,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="8"/>
@@ -4728,11 +4755,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="12"/>
@@ -5015,6 +5042,12 @@
         <v>90</v>
       </c>
       <c r="GR9" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU9">
+        <v>90</v>
+      </c>
+      <c r="GV9" t="s">
         <v>110</v>
       </c>
       <c r="HC9">
@@ -5086,11 +5119,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="37"/>
-        <v>1923</v>
+        <v>2013</v>
       </c>
       <c r="C10">
         <f t="shared" si="2"/>
-        <v>1323</v>
+        <v>1413</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -5106,11 +5139,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="8"/>
@@ -5122,11 +5155,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="12"/>
@@ -5382,6 +5415,12 @@
         <v>85</v>
       </c>
       <c r="GR10" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU10">
+        <v>90</v>
+      </c>
+      <c r="GV10" t="s">
         <v>110</v>
       </c>
       <c r="HD10" t="s">
@@ -5456,11 +5495,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="37"/>
-        <v>1268</v>
+        <v>1313</v>
       </c>
       <c r="C11">
         <f t="shared" si="2"/>
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -5476,7 +5515,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="7"/>
@@ -5484,7 +5523,7 @@
       </c>
       <c r="I11" s="3">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="9"/>
@@ -5492,7 +5531,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="11"/>
@@ -5500,7 +5539,7 @@
       </c>
       <c r="M11" s="3">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="13"/>
@@ -5731,6 +5770,12 @@
         <v>5</v>
       </c>
       <c r="GR11" t="s">
+        <v>136</v>
+      </c>
+      <c r="GU11">
+        <v>45</v>
+      </c>
+      <c r="GV11" t="s">
         <v>136</v>
       </c>
       <c r="GY11">
@@ -6296,6 +6341,9 @@
       <c r="GR13" t="s">
         <v>139</v>
       </c>
+      <c r="GV13" t="s">
+        <v>139</v>
+      </c>
       <c r="HD13" t="s">
         <v>139</v>
       </c>
@@ -6316,11 +6364,11 @@
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="33"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="34"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="35"/>
@@ -6341,11 +6389,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="37"/>
-        <v>2345</v>
+        <v>2360</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>1247</v>
+        <v>1262</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
@@ -6361,7 +6409,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="7"/>
@@ -6369,7 +6417,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="9"/>
@@ -6377,7 +6425,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="11"/>
@@ -6385,7 +6433,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="13"/>
@@ -6677,6 +6725,12 @@
       </c>
       <c r="GR14" t="s">
         <v>110</v>
+      </c>
+      <c r="GU14">
+        <v>15</v>
+      </c>
+      <c r="GV14" t="s">
+        <v>136</v>
       </c>
       <c r="GY14">
         <v>90</v>
@@ -6771,11 +6825,11 @@
       </c>
       <c r="B15">
         <f t="shared" si="37"/>
-        <v>1753</v>
+        <v>1814</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
-        <v>1016</v>
+        <v>1077</v>
       </c>
       <c r="D15">
         <f t="shared" si="3"/>
@@ -6791,11 +6845,11 @@
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="8"/>
@@ -6807,11 +6861,11 @@
       </c>
       <c r="K15">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="3">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M15" s="3">
         <f t="shared" si="12"/>
@@ -7112,6 +7166,12 @@
         <v>90</v>
       </c>
       <c r="GR15" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU15">
+        <v>61</v>
+      </c>
+      <c r="GV15" t="s">
         <v>110</v>
       </c>
       <c r="GY15">
@@ -7830,11 +7890,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="37"/>
-        <v>1751</v>
+        <v>1818</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
-        <v>1117</v>
+        <v>1184</v>
       </c>
       <c r="D18">
         <f t="shared" si="3"/>
@@ -7850,11 +7910,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="8"/>
@@ -7866,11 +7926,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="12"/>
@@ -7914,11 +7974,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="23"/>
@@ -7930,7 +7990,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -8157,6 +8217,15 @@
       </c>
       <c r="GS18">
         <v>1</v>
+      </c>
+      <c r="GU18">
+        <v>67</v>
+      </c>
+      <c r="GV18" t="s">
+        <v>110</v>
+      </c>
+      <c r="GW18">
+        <v>2</v>
       </c>
       <c r="GY18">
         <v>18</v>
@@ -8233,11 +8302,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="37"/>
-        <v>1330</v>
+        <v>1353</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="D19">
         <f t="shared" si="3"/>
@@ -8253,7 +8322,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="7"/>
@@ -8261,7 +8330,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="9"/>
@@ -8269,7 +8338,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="11"/>
@@ -8277,7 +8346,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="13"/>
@@ -8518,6 +8587,12 @@
       </c>
       <c r="GS19">
         <v>1</v>
+      </c>
+      <c r="GU19">
+        <v>23</v>
+      </c>
+      <c r="GV19" t="s">
+        <v>136</v>
       </c>
       <c r="GY19">
         <v>72</v>
@@ -8949,6 +9024,9 @@
       <c r="GR20" t="s">
         <v>139</v>
       </c>
+      <c r="GV20" t="s">
+        <v>139</v>
+      </c>
       <c r="GY20">
         <v>31</v>
       </c>
@@ -9005,11 +9083,11 @@
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="34"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="35"/>
@@ -9268,11 +9346,11 @@
       </c>
       <c r="B22">
         <f t="shared" si="37"/>
-        <v>2851</v>
+        <v>2926</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
-        <v>1832</v>
+        <v>1907</v>
       </c>
       <c r="D22">
         <f t="shared" si="3"/>
@@ -9288,11 +9366,11 @@
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="8"/>
@@ -9304,11 +9382,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M22" s="3">
         <f t="shared" si="12"/>
@@ -9360,11 +9438,11 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="23"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22" s="4">
         <f t="shared" si="24"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <f t="shared" si="25"/>
@@ -9372,7 +9450,7 @@
       </c>
       <c r="AB22">
         <f t="shared" si="26"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <f t="shared" si="27"/>
@@ -9601,6 +9679,15 @@
       </c>
       <c r="GR22" t="s">
         <v>139</v>
+      </c>
+      <c r="GU22">
+        <v>75</v>
+      </c>
+      <c r="GV22" t="s">
+        <v>110</v>
+      </c>
+      <c r="GX22">
+        <v>1</v>
       </c>
       <c r="GY22">
         <v>90</v>
@@ -9903,11 +9990,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="37"/>
-        <v>2582</v>
+        <v>2672</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
-        <v>1890</v>
+        <v>1980</v>
       </c>
       <c r="D24">
         <f t="shared" si="3"/>
@@ -9923,11 +10010,11 @@
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3">
         <f t="shared" si="8"/>
@@ -9939,11 +10026,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="11"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" s="3">
         <f t="shared" si="12"/>
@@ -10205,6 +10292,12 @@
         <v>90</v>
       </c>
       <c r="GR24" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU24">
+        <v>90</v>
+      </c>
+      <c r="GV24" t="s">
         <v>110</v>
       </c>
       <c r="GY24">
@@ -10851,6 +10944,9 @@
       <c r="GT26">
         <v>1</v>
       </c>
+      <c r="GV26" t="s">
+        <v>139</v>
+      </c>
       <c r="GY26">
         <v>72</v>
       </c>
@@ -10934,11 +11030,11 @@
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="33"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="34"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="35"/>
@@ -10959,11 +11055,11 @@
       </c>
       <c r="B27">
         <f t="shared" si="37"/>
-        <v>2107</v>
+        <v>2197</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
-        <v>1612</v>
+        <v>1702</v>
       </c>
       <c r="D27">
         <f t="shared" si="3"/>
@@ -10979,11 +11075,11 @@
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="8"/>
@@ -10995,11 +11091,11 @@
       </c>
       <c r="K27">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M27" s="3">
         <f t="shared" si="12"/>
@@ -11222,6 +11318,12 @@
         <v>90</v>
       </c>
       <c r="GR27" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU27">
+        <v>90</v>
+      </c>
+      <c r="GV27" t="s">
         <v>110</v>
       </c>
       <c r="HD27" t="s">
@@ -11501,6 +11603,9 @@
       <c r="FX28" t="s">
         <v>139</v>
       </c>
+      <c r="GV28" t="s">
+        <v>139</v>
+      </c>
       <c r="GY28">
         <v>79</v>
       </c>
@@ -11575,11 +11680,11 @@
       </c>
       <c r="PS28" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT28" s="3">
         <f t="shared" si="34"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU28" s="3">
         <f t="shared" si="35"/>
@@ -11600,11 +11705,11 @@
       </c>
       <c r="B29">
         <f t="shared" si="37"/>
-        <v>1366</v>
+        <v>1456</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
-        <v>1126</v>
+        <v>1216</v>
       </c>
       <c r="D29">
         <f t="shared" si="3"/>
@@ -11620,11 +11725,11 @@
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" si="8"/>
@@ -11636,11 +11741,11 @@
       </c>
       <c r="K29">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="11"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" si="12"/>
@@ -11851,6 +11956,12 @@
         <v>90</v>
       </c>
       <c r="GR29" t="s">
+        <v>110</v>
+      </c>
+      <c r="GU29">
+        <v>90</v>
+      </c>
+      <c r="GV29" t="s">
         <v>110</v>
       </c>
       <c r="HC29">
@@ -12115,6 +12226,9 @@
       <c r="GR30" t="s">
         <v>139</v>
       </c>
+      <c r="GV30" t="s">
+        <v>139</v>
+      </c>
       <c r="KI30">
         <v>90</v>
       </c>
@@ -12129,11 +12243,11 @@
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="99">COUNTIF(AI30:PR30,"HG")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="100">COUNTIF(CY30:GX30,"HG")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="101">COUNTIF(GY30:IT30,"HG")</f>
@@ -12154,11 +12268,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="104">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>860</v>
+        <v>950</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="105">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>860</v>
+        <v>950</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="106">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -12174,11 +12288,11 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="109">SUM(H31:I31)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="110">COUNTIF(AI31:PR31,"T")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="111">COUNTIF(AI31:PR31,"R")</f>
@@ -12190,11 +12304,11 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="113">SUM(L31:M31)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="114">COUNTIF(CY31:GX31,"T")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="115">COUNTIF(CY31:GX31,"R")</f>
@@ -12238,27 +12352,27 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" ref="W31" si="125">SUM(AK31,AO31,AS31,AW31,BA31,BE31,BI31,BM31,BQ31,BU31,BY31,CC31,CG31,CK31,CO31,CS31,CW31,DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X31" s="4">
         <f t="shared" ref="X31" si="126">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31,HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31,IW31,JA31,JE31,JI31,JM31,JQ31,JU31,JY31,KC31,KG31,KK31,KO31,KS31,KW31,LA31,LE31,LI31,LM31,LQ31,LU31,LY31,MC31,MG31,MK31,MO31,MS31,MW31,NA31,NE31,NI31,NM31,NQ31,NU31,NY31,OC31,OG31,OK31,OO31,OS31,OW31,PA31,PE31,PI31,PM31,PQ31)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y31" s="4">
         <f t="shared" ref="Y31" si="127">SUM(AL31,AP31,AT31,AX31,BB31,BF31,BJ31,BN31,BR31,BV31,BZ31,CD31,CH31,CL31,CP31,CT31,CX31,DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z31" s="4">
         <f t="shared" ref="Z31" si="128">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31,HB31,HF31,HJ31,HN31,HR31,HV31,HZ31,ID31,IH31,IL31,IP31,IT31,IX31,JB31,JF31,JJ31,JN31,JR31,JV31,JZ31,KD31,KH31,KL31,KP31,KT31,KX31,LB31,LF31,LJ31,LN31,LR31,LV31,LZ31,MD31,MH31,ML31,MP31,MT31,MX31,NB31,NF31,NJ31,NN31,NR31,NV31,NZ31,OD31,OH31,OL31,OP31,OT31,OX31,PB31,PF31,PJ31,PN31,PR31)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <f t="shared" ref="AA31" si="129">SUM(DA31,DE31,DI31,DM31,DQ31,DU31,DY31,EC31,EG31,EK31,EO31,ES31,EW31,FA31,FE31,FI31,FM31,FQ31,FU31,FY31,GC31,GG31,GK31,GO31,GS31,GW31)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB31">
         <f t="shared" ref="AB31" si="130">SUM(DB31,DF31,DJ31,DN31,DR31,DV31,DZ31,ED31,EH31,EL31,EP31,ET31,EX31,FB31,FF31,FJ31,FN31,FR31,FV31,FZ31,GD31,GH31,GL31,GP31,GT31,GX31)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <f t="shared" ref="AC31" si="131">SUM(HA31,HE31,HI31,HM31,HQ31,HU31,HY31,IC31,IG31,IK31,IO31,IS31)</f>
@@ -12381,6 +12495,18 @@
         <v>2</v>
       </c>
       <c r="GT31">
+        <v>1</v>
+      </c>
+      <c r="GU31">
+        <v>90</v>
+      </c>
+      <c r="GV31" t="s">
+        <v>110</v>
+      </c>
+      <c r="GW31">
+        <v>1</v>
+      </c>
+      <c r="GX31">
         <v>1</v>
       </c>
       <c r="PS31" s="3">
@@ -12410,11 +12536,11 @@
       </c>
       <c r="B32">
         <f t="shared" ref="B32" si="142">SUM(AI32,AM32,AQ32,AU32,AY32,BC32,BG32,BK32,BO32,BS32,BW32,CA32,CE32,CI32,CM32,CQ32,CU32,CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32,GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32,IU32,IY32,JC32,JG32,JK32,JO32,JS32,JW32,KA32,KE32,KI32,KM32,KQ32,KU32,KY32,LC32,LG32,LK32,LO32,LS32,LW32,MA32,ME32,MI32,MM32,MQ32,MU32,MY32,NC32,NG32,NK32,NO32,NS32,NW32,OA32,OE32,OI32,OM32,OQ32,OU32,OY32,PC32,PG32,PK32,PO32)</f>
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="C32">
         <f t="shared" ref="C32" si="143">SUM(CY32,DC32,DG32,DK32,DO32,DS32,DW32,EA32,EE32,EI32,EM32,EQ32,EU32,EY32,FC32,FG32,FK32,FO32,FS32,FW32,GA32,GE32,GI32,GM32,GQ32,GU32)</f>
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32" si="144">SUM(GY32,HC32,HG32,HK32,HO32,HS32,HW32,IA32,IE32,II32,IM32,IQ32)</f>
@@ -12430,7 +12556,7 @@
       </c>
       <c r="G32">
         <f t="shared" ref="G32" si="147">SUM(H32:I32)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" ref="H32" si="148">COUNTIF(AI32:PR32,"T")</f>
@@ -12438,7 +12564,7 @@
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32" si="149">COUNTIF(AI32:PR32,"R")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="3">
         <f t="shared" ref="J32" si="150">COUNTIF(AI32:PR32,"NR")</f>
@@ -12446,7 +12572,7 @@
       </c>
       <c r="K32">
         <f t="shared" ref="K32" si="151">SUM(L32:M32)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" ref="L32" si="152">COUNTIF(CY32:GX32,"T")</f>
@@ -12454,7 +12580,7 @@
       </c>
       <c r="M32" s="3">
         <f t="shared" ref="M32" si="153">COUNTIF(CY32:GX32,"R")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N32" s="3">
         <f t="shared" ref="N32" si="154">COUNTIF(CY32:GX32,"NR")</f>
@@ -12620,6 +12746,12 @@
       </c>
       <c r="GR32" t="s">
         <v>110</v>
+      </c>
+      <c r="GU32">
+        <v>29</v>
+      </c>
+      <c r="GV32" t="s">
+        <v>136</v>
       </c>
       <c r="KQ32">
         <v>90</v>
